--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{055AAB22-1095-4B6C-8FB3-682B4E6E9188}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFEA699-F64F-49D5-8C93-113698B787A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="540" yWindow="1140" windowWidth="28770" windowHeight="15570" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
+    <sheet name="NL" sheetId="2" r:id="rId2"/>
+    <sheet name="FR" sheetId="3" r:id="rId3"/>
+    <sheet name="SP" sheetId="4" r:id="rId4"/>
+    <sheet name="IT" sheetId="5" r:id="rId5"/>
+    <sheet name="GE" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="410">
   <si>
     <t>type</t>
   </si>
@@ -259,13 +269,1015 @@
   </si>
   <si>
     <t>Physical activity, rest and asking for support contribute to well-being. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Wat is het belangrijkste idee achter SDG 3 – Goede gezondheid en welzijn?</t>
+  </si>
+  <si>
+    <t>Makkelijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Het richt zich op gezondheid en veiligheid op het werk.</t>
+  </si>
+  <si>
+    <t>Het is alleen van toepassing op nationale overheden.</t>
+  </si>
+  <si>
+    <t>Het vraagt bedrijven om langetermijneffecten te negeren.</t>
+  </si>
+  <si>
+    <t>Het is slechts een marketingslogan zonder praktische betekenis.</t>
+  </si>
+  <si>
+    <t>SDG 3 gaat over gezondheid en veiligheid op het werk en over het omzetten van dat doel in concrete actie. SDG 3 wordt nuttig wanneer mensen het brede doel vertalen naar praktische beslissingen.</t>
+  </si>
+  <si>
+    <t>Oké</t>
+  </si>
+  <si>
+    <t>Waarom is SDG 3 relevant voor een bedrijf dat chemische producten distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen in jaarverslagen thuishoort.</t>
+  </si>
+  <si>
+    <t>Omdat het veilig omgaan met chemicaliën de duurzaamheidsprestaties kan beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat chemicaliën geen verband houden met duurzaamheid.</t>
+  </si>
+  <si>
+    <t>Veilig omgaan met chemicaliën is een praktisch gebied waarop een bedrijf verschil kan maken. De SDG's verbinden wereldwijde doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 3?</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen bijdragen door kleine gewoonten.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>Alleen ziekenhuizen zijn verantwoordelijk voor gezondheid.</t>
+  </si>
+  <si>
+    <t>SDG 3 kan worden gekoppeld aan dagelijkse beslissingen.</t>
+  </si>
+  <si>
+    <t>Dit is het misverstand: het maakt de SDG te beperkt en verhult praktische mogelijkheden. Een goede quizvraag stelt vaak een misvatting ter discussie, omdat dit de leerstof beter doet beklijven.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 3 het beste om van theorie naar praktijk?</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die daadwerkelijk uitvoeren.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn van duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Wat maakt SDG 3 een nuttig leerthema voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het koppelt wereldwijde uitdagingen aan keuzes die mensen op het werk en thuis herkennen.</t>
+  </si>
+  <si>
+    <t>Het geeft voor elke situatie één perfect antwoord.</t>
+  </si>
+  <si>
+    <t>Het maakt deskundige kennis overbodig.</t>
+  </si>
+  <si>
+    <t>Het houdt geen verband met de bedrijfscultuur.</t>
+  </si>
+  <si>
+    <t>Mensen leren het meest wanneer ze het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG's zijn het meest aansprekend wanneer ze relevant en concreet aanvoelen en aansluiten bij de rollen van mensen.</t>
+  </si>
+  <si>
+    <t>Wat is de uitgesproken ambitie van STOCKMEIER op het gebied van veiligheid?</t>
+  </si>
+  <si>
+    <t>Alle veiligheidstrainingen vervangen door posters</t>
+  </si>
+  <si>
+    <t>Nul werkgerelateerde ongevallen</t>
+  </si>
+  <si>
+    <t>Alleen ongevallen op kantoor verminderen</t>
+  </si>
+  <si>
+    <t>Ongevallen accepteren als productiedoelen worden gehaald</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt de ambitie van nul werkgerelateerde ongevallen en nul schadelijke gevolgen voor de gezondheid. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welk gerapporteerd resultaat ondersteunt het toezicht op de gezondheid op het werk?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Ongevallen worden niet geregistreerd</t>
+  </si>
+  <si>
+    <t>Alleen managers ontvangen veiligheidsinformatie</t>
+  </si>
+  <si>
+    <t>100% van de mensen valt onder gezondheids- en veiligheidsmanagementsystemen</t>
+  </si>
+  <si>
+    <t>Veiligheid wordt slechts eens in de tien jaar gemeten</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat 100% van de mensen onder gezondheids- en veiligheidsmanagementsystemen valt. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke actie van Gamma Chimica is een praktische veiligheidsverbetering?</t>
+  </si>
+  <si>
+    <t>Minder communiceren over risico's</t>
+  </si>
+  <si>
+    <t>Stoppen met het melden van bijna-ongevallen</t>
+  </si>
+  <si>
+    <t>Alle werkinstructies verwijderen</t>
+  </si>
+  <si>
+    <t>Beschermende barrières en valbeveiligingssystemen</t>
+  </si>
+  <si>
+    <t>Het rapport belicht beschermende barrières, valbeveiliging en duidelijkere werkinstructies met afbeeldingen bij Gamma Chimica. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Kan worden verbeterd</t>
+  </si>
+  <si>
+    <t>Welke gewoonte thuis ondersteunt SDG 3 het beste?</t>
+  </si>
+  <si>
+    <t>Chemicaliën en medicijnen veilig opbergen</t>
+  </si>
+  <si>
+    <t>Waarschuwingsetiketten negeren</t>
+  </si>
+  <si>
+    <t>Gevaren voor iemand anders laten liggen</t>
+  </si>
+  <si>
+    <t>Schoonmaakmiddelen mengen om ze sterker te maken</t>
+  </si>
+  <si>
+    <t>Veilige opslag voorkomt ongevallen en beschermt mensen thuis. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Welke keuze in het privéleven draagt bij aan welzijn?</t>
+  </si>
+  <si>
+    <t>Nooit om hulp vragen</t>
+  </si>
+  <si>
+    <t>Regelmatig bewegen en voldoende rusten</t>
+  </si>
+  <si>
+    <t>Altijd pauzes overslaan</t>
+  </si>
+  <si>
+    <t>Stresssignalen negeren</t>
+  </si>
+  <si>
+    <t>Lichaamsbeweging, rust en om steun vragen dragen bij aan welzijn. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
+    <t>Column8</t>
+  </si>
+  <si>
+    <t>Column9</t>
+  </si>
+  <si>
+    <t>Column10</t>
+  </si>
+  <si>
+    <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
+  </si>
+  <si>
+    <t>Leicht · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf Gesundheit und Sicherheit am Arbeitsplatz.</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Bei SDG 3 geht es um Gesundheit und Sicherheit am Arbeitsplatz und darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 3 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 3 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil der sichere Umgang mit Chemikalien die Nachhaltigkeitsleistung beeinflussen kann.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Der sichere Umgang mit Chemikalien ist ein praktischer Bereich, in dem ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 3?</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten einen Beitrag leisten.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>Nur Krankenhäuser sind für Gesundheit verantwortlich.</t>
+  </si>
+  <si>
+    <t>SDG 3 lässt sich mit täglichen Entscheidungen verknüpfen.</t>
+  </si>
+  <si>
+    <t>Das ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Möglichkeiten. Eine gute Quizfrage hinterfragt häufig ein Missverständnis, weil dadurch das Gelernte besser im Gedächtnis bleibt.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 3 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand kontrolliert.</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles in Ordnung bringt.</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln ermöglicht Lernen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu einer praktischen Verhaltensänderung führen.</t>
+  </si>
+  <si>
+    <t>Was macht SDG 3 zu einem nützlichen Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen bei der Arbeit und zu Hause kennen.</t>
+  </si>
+  <si>
+    <t>Es liefert für jede Situation eine einzige perfekte Antwort.</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Es hat keinen Bezug zur Unternehmenskultur.</t>
+  </si>
+  <si>
+    <t>Am meisten lernen Menschen, wenn sie den Zusammenhang zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind besonders ansprechend, wenn sie relevant und konkret wirken und mit den Rollen der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches Ziel hat STOCKMEIER in Bezug auf Sicherheit formuliert?</t>
+  </si>
+  <si>
+    <t>Alle Sicherheitsschulungen durch Plakate ersetzen</t>
+  </si>
+  <si>
+    <t>Null arbeitsbedingte Unfälle</t>
+  </si>
+  <si>
+    <t>Nur Unfälle in Büros reduzieren</t>
+  </si>
+  <si>
+    <t>Unfälle akzeptieren, wenn Produktionsziele erreicht werden</t>
+  </si>
+  <si>
+    <t>Der Bericht nennt das Ziel von null arbeitsbedingten Unfällen und null gesundheitsschädlichen Auswirkungen. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches berichtete Ergebnis unterstützt die Überwachung der Gesundheit am Arbeitsplatz?</t>
+  </si>
+  <si>
+    <t>Schwer · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Unfälle werden nicht erfasst</t>
+  </si>
+  <si>
+    <t>Nur Führungskräfte erhalten Sicherheitsinformationen</t>
+  </si>
+  <si>
+    <t>100 % der Menschen werden von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst</t>
+  </si>
+  <si>
+    <t>Sicherheit wird nur einmal alle zehn Jahre gemessen</t>
+  </si>
+  <si>
+    <t>Der Bericht besagt, dass 100 % der Menschen von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst werden. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Maßnahme von Gamma Chimica ist eine praktische Sicherheitsverbesserung?</t>
+  </si>
+  <si>
+    <t>Weniger über Risiken kommunizieren</t>
+  </si>
+  <si>
+    <t>Die Meldung von Beinaheunfällen einstellen</t>
+  </si>
+  <si>
+    <t>Alle Arbeitsanweisungen entfernen</t>
+  </si>
+  <si>
+    <t>Schutzbarrieren und Absturzsicherungssysteme</t>
+  </si>
+  <si>
+    <t>Der Bericht hebt Schutzbarrieren, Absturzsicherungen und klarere bildgestützte Arbeitsanweisungen bei Gamma Chimica hervor. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Kann verbessert werden</t>
+  </si>
+  <si>
+    <t>Welche Gewohnheit zu Hause unterstützt SDG 3 am besten?</t>
+  </si>
+  <si>
+    <t>Chemikalien und Medikamente sicher aufbewahren</t>
+  </si>
+  <si>
+    <t>Warnhinweise ignorieren</t>
+  </si>
+  <si>
+    <t>Gefahren für jemand anderen liegen lassen</t>
+  </si>
+  <si>
+    <t>Reinigungsmittel mischen, um sie stärker zu machen</t>
+  </si>
+  <si>
+    <t>Eine sichere Aufbewahrung verhindert Unfälle und schützt Menschen zu Hause. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Welche Entscheidung im Privatleben trägt zum Wohlbefinden bei?</t>
+  </si>
+  <si>
+    <t>Nie um Hilfe bitten</t>
+  </si>
+  <si>
+    <t>Regelmäßige Bewegung und ausreichend Erholung</t>
+  </si>
+  <si>
+    <t>Pausen immer auslassen</t>
+  </si>
+  <si>
+    <t>Stresssignale ignorieren</t>
+  </si>
+  <si>
+    <t>Körperliche Aktivität, Erholung und die Bitte um Unterstützung tragen zum Wohlbefinden bei. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Quelle est l'idée principale de l'ODD 3 – Bonne santé et bien-être ?</t>
+  </si>
+  <si>
+    <t>Facile · Choix unique</t>
+  </si>
+  <si>
+    <t>Il porte sur la santé et la sécurité au travail.</t>
+  </si>
+  <si>
+    <t>Il s'applique uniquement aux gouvernements nationaux.</t>
+  </si>
+  <si>
+    <t>Il demande aux entreprises d'ignorer les impacts à long terme.</t>
+  </si>
+  <si>
+    <t>Ce n'est qu'un slogan marketing sans signification pratique.</t>
+  </si>
+  <si>
+    <t>L'ODD 3 concerne la santé et la sécurité au travail ainsi que la mise en œuvre concrète de cet objectif. L'ODD 3 devient utile lorsque les personnes traduisent cet objectif général en décisions pratiques.</t>
+  </si>
+  <si>
+    <t>D'accord</t>
+  </si>
+  <si>
+    <t>Pourquoi l'ODD 3 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité ne concerne que les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que la manipulation sûre des produits chimiques peut influencer la performance en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n'ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>La manipulation sûre des produits chimiques est un domaine concret dans lequel une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante au sujet de l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Les collaborateurs peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>Seuls les hôpitaux sont responsables de la santé.</t>
+  </si>
+  <si>
+    <t>L'ODD 3 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>Voici l'idée fausse : elle réduit trop la portée de l'ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée reçue, car cela rend l'apprentissage mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement permet le mieux de faire passer l'ODD 3 de la théorie à l'action ?</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne vérifie.</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu'un d'autre règle tout.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mener à bien.</t>
+  </si>
+  <si>
+    <t>Une action concrète favorise l'apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Pourquoi l'ODD 3 constitue-t-il un sujet d'apprentissage utile pour les collaborateurs ?</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Il fournit une réponse parfaite pour chaque situation.</t>
+  </si>
+  <si>
+    <t>Il supprime la nécessité de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>Il n'a aucun rapport avec la culture d'entreprise.</t>
+  </si>
+  <si>
+    <t>L'apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et des choix familiers. Les ODD sont plus motivants lorsqu'ils paraissent pertinents, concrets et liés au rôle de chacun.</t>
+  </si>
+  <si>
+    <t>Quelle est l'ambition déclarée de STOCKMEIER en matière de sécurité ?</t>
+  </si>
+  <si>
+    <t>Remplacer toutes les formations à la sécurité par des affiches</t>
+  </si>
+  <si>
+    <t>Zéro accident lié au travail</t>
+  </si>
+  <si>
+    <t>Réduire uniquement les accidents dans les bureaux</t>
+  </si>
+  <si>
+    <t>Accepter les accidents si les objectifs de production sont atteints</t>
+  </si>
+  <si>
+    <t>Le rapport énonce une ambition de zéro accident lié au travail et de zéro effet nocif sur la santé. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quel résultat communiqué soutient le suivi de la santé au travail ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>Les accidents ne sont pas enregistrés</t>
+  </si>
+  <si>
+    <t>Seuls les responsables reçoivent des informations sur la sécurité</t>
+  </si>
+  <si>
+    <t>100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité</t>
+  </si>
+  <si>
+    <t>La sécurité n'est mesurée qu'une fois tous les dix ans</t>
+  </si>
+  <si>
+    <t>Le rapport indique que 100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quelle action de Gamma Chimica constitue une amélioration concrète de la sécurité ?</t>
+  </si>
+  <si>
+    <t>Réduire la communication sur les risques</t>
+  </si>
+  <si>
+    <t>Cesser de signaler les quasi-accidents</t>
+  </si>
+  <si>
+    <t>Supprimer toutes les instructions de travail</t>
+  </si>
+  <si>
+    <t>Des barrières de protection et des systèmes antichute</t>
+  </si>
+  <si>
+    <t>Le rapport met en avant les barrières de protection, les systèmes antichute et des instructions de travail illustrées plus claires chez Gamma Chimica. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Peut être amélioré</t>
+  </si>
+  <si>
+    <t>À la maison, quelle habitude soutient le mieux l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Ranger les produits chimiques et les médicaments en toute sécurité</t>
+  </si>
+  <si>
+    <t>Ignorer les étiquettes d'avertissement</t>
+  </si>
+  <si>
+    <t>Laisser les dangers à quelqu'un d'autre</t>
+  </si>
+  <si>
+    <t>Mélanger des produits de nettoyage pour les rendre plus puissants</t>
+  </si>
+  <si>
+    <t>Un rangement sûr prévient les accidents et protège les personnes à la maison. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Quel choix dans la vie privée contribue au bien-être ?</t>
+  </si>
+  <si>
+    <t>Ne jamais demander d'aide</t>
+  </si>
+  <si>
+    <t>Bouger régulièrement et se reposer suffisamment</t>
+  </si>
+  <si>
+    <t>Toujours sauter les pauses</t>
+  </si>
+  <si>
+    <t>Ignorer les signes de stress</t>
+  </si>
+  <si>
+    <t>L'activité physique, le repos et le fait de demander du soutien contribuent au bien-être. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>¿Cuál es la idea principal del ODS 3 – Salud y bienestar?</t>
+  </si>
+  <si>
+    <t>Fácil · Opción única</t>
+  </si>
+  <si>
+    <t>Se centra en la salud y la seguridad en el trabajo.</t>
+  </si>
+  <si>
+    <t>Solo se aplica a los gobiernos nacionales.</t>
+  </si>
+  <si>
+    <t>Pide a las empresas que ignoren los impactos a largo plazo.</t>
+  </si>
+  <si>
+    <t>Es solo un eslogan de marketing sin significado práctico.</t>
+  </si>
+  <si>
+    <t>El ODS 3 trata sobre la salud y la seguridad en el trabajo y sobre convertir ese objetivo en acciones concretas. El ODS 3 resulta útil cuando las personas traducen el objetivo general en decisiones prácticas.</t>
+  </si>
+  <si>
+    <t>De acuerdo</t>
+  </si>
+  <si>
+    <t>¿Por qué es relevante el ODS 3 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Medio · Opción única</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo pertenece a los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque la manipulación segura de productos químicos puede influir en el desempeño en sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>La manipulación segura de productos químicos es un ámbito práctico en el que una empresa puede marcar la diferencia. Los ODS conectan los objetivos globales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido habitual sobre el ODS 3?</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>Solo los hospitales son responsables de la salud.</t>
+  </si>
+  <si>
+    <t>El ODS 3 puede vincularse a las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: limita demasiado el ODS y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar una idea errónea, porque así el aprendizaje resulta memorable.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 3 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está comprobándolo.</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>Esperar hasta que otra persona lo solucione todo.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio de comportamiento práctico.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 3 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>Relaciona los desafíos globales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura empresarial.</t>
+  </si>
+  <si>
+    <t>El aprendizaje es más sólido cuando las personas ven el vínculo entre los objetivos globales y las decisiones conocidas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y conectados con las funciones de las personas.</t>
+  </si>
+  <si>
+    <t>¿Cuál es la ambición declarada de STOCKMEIER en relación con la seguridad?</t>
+  </si>
+  <si>
+    <t>Sustituir toda la formación en seguridad por carteles</t>
+  </si>
+  <si>
+    <t>Cero accidentes laborales</t>
+  </si>
+  <si>
+    <t>Reducir únicamente los accidentes en las oficinas</t>
+  </si>
+  <si>
+    <t>Aceptar accidentes si se cumplen los objetivos de producción</t>
+  </si>
+  <si>
+    <t>El informe establece la ambición de cero accidentes laborales y cero efectos perjudiciales para la salud. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué resultado comunicado respalda el seguimiento de la salud laboral?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>Los accidentes no se registran</t>
+  </si>
+  <si>
+    <t>Solo los directivos reciben información sobre seguridad</t>
+  </si>
+  <si>
+    <t>El 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad</t>
+  </si>
+  <si>
+    <t>La seguridad se mide solo una vez cada diez años</t>
+  </si>
+  <si>
+    <t>El informe indica que el 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué acción de Gamma Chimica supone una mejora práctica de la seguridad?</t>
+  </si>
+  <si>
+    <t>Reducir la comunicación sobre los riesgos</t>
+  </si>
+  <si>
+    <t>Dejar de informar sobre cuasiaccidentes</t>
+  </si>
+  <si>
+    <t>Eliminar todas las instrucciones de trabajo</t>
+  </si>
+  <si>
+    <t>Barreras de protección y sistemas anticaídas</t>
+  </si>
+  <si>
+    <t>El informe destaca las barreras de protección, los sistemas anticaídas y unas instrucciones de trabajo con imágenes más claras en Gamma Chimica. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>Puede mejorarse</t>
+  </si>
+  <si>
+    <t>En casa, ¿qué hábito apoya mejor el ODS 3?</t>
+  </si>
+  <si>
+    <t>Guardar de forma segura los productos químicos y los medicamentos</t>
+  </si>
+  <si>
+    <t>Ignorar las etiquetas de advertencia</t>
+  </si>
+  <si>
+    <t>Dejar los peligros para otra persona</t>
+  </si>
+  <si>
+    <t>Mezclar productos de limpieza para hacerlos más fuertes</t>
+  </si>
+  <si>
+    <t>El almacenamiento seguro evita accidentes y protege a las personas en casa. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Qué elección en la vida privada contribuye al bienestar?</t>
+  </si>
+  <si>
+    <t>No pedir ayuda nunca</t>
+  </si>
+  <si>
+    <t>Actividad física regular y descanso adecuado</t>
+  </si>
+  <si>
+    <t>Saltarse siempre las pausas</t>
+  </si>
+  <si>
+    <t>Ignorar las señales de estrés</t>
+  </si>
+  <si>
+    <t>La actividad física, el descanso y pedir apoyo contribuyen al bienestar. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>Qual è l'idea principale alla base dell'SDG 3 – Salute e benessere?</t>
+  </si>
+  <si>
+    <t>Facile · Risposta singola</t>
+  </si>
+  <si>
+    <t>Si concentra sulla salute e sulla sicurezza sul lavoro.</t>
+  </si>
+  <si>
+    <t>Si applica soltanto ai governi nazionali.</t>
+  </si>
+  <si>
+    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
+  </si>
+  <si>
+    <t>È solo uno slogan di marketing senza significato pratico.</t>
+  </si>
+  <si>
+    <t>L'SDG 3 riguarda la salute e la sicurezza sul lavoro e la trasformazione di questo obiettivo in azioni concrete. L'SDG 3 diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Va bene</t>
+  </si>
+  <si>
+    <t>Perché l'SDG 3 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Risposta singola</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità riguarda soltanto i rapporti annuali.</t>
+  </si>
+  <si>
+    <t>Perché la manipolazione sicura dei prodotti chimici può influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli SDG sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>La manipolazione sicura dei prodotti chimici è un ambito concreto in cui un'azienda può fare la differenza. Gli SDG collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull'SDG 3?</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>Solo gli ospedali sono responsabili della salute.</t>
+  </si>
+  <si>
+    <t>L'SDG 3 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo l'SDG e nasconde opportunità concrete. Una buona domanda di un quiz spesso mette in discussione un'idea errata, perché rende memorabile l'apprendimento.</t>
+  </si>
+  <si>
+    <t>Quale comportamento trasforma meglio l'SDG 3 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico del comportamento.</t>
+  </si>
+  <si>
+    <t>Cosa rende l'SDG 3 un argomento formativo utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Fornisce una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>Non ha alcun rapporto con la cultura aziendale.</t>
+  </si>
+  <si>
+    <t>L'apprendimento è più efficace quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli SDG sono più coinvolgenti quando appaiono rilevanti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Qual è l'ambizione dichiarata di STOCKMEIER in materia di sicurezza?</t>
+  </si>
+  <si>
+    <t>Sostituire tutta la formazione sulla sicurezza con poster</t>
+  </si>
+  <si>
+    <t>Zero infortuni sul lavoro</t>
+  </si>
+  <si>
+    <t>Ridurre soltanto gli incidenti negli uffici</t>
+  </si>
+  <si>
+    <t>Accettare gli incidenti se vengono raggiunti gli obiettivi di produzione</t>
+  </si>
+  <si>
+    <t>Il rapporto dichiara l'ambizione di zero infortuni sul lavoro e zero effetti nocivi sulla salute. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale risultato riportato supporta il monitoraggio della salute sul lavoro?</t>
+  </si>
+  <si>
+    <t>Difficile · Risposta singola</t>
+  </si>
+  <si>
+    <t>Gli incidenti non vengono registrati</t>
+  </si>
+  <si>
+    <t>Solo i dirigenti ricevono informazioni sulla sicurezza</t>
+  </si>
+  <si>
+    <t>Il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza</t>
+  </si>
+  <si>
+    <t>La sicurezza viene misurata soltanto una volta ogni dieci anni</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale azione di Gamma Chimica rappresenta un miglioramento pratico della sicurezza?</t>
+  </si>
+  <si>
+    <t>Ridurre la comunicazione sui rischi</t>
+  </si>
+  <si>
+    <t>Interrompere la segnalazione dei mancati incidenti</t>
+  </si>
+  <si>
+    <t>Rimuovere tutte le istruzioni di lavoro</t>
+  </si>
+  <si>
+    <t>Barriere protettive e sistemi anticaduta</t>
+  </si>
+  <si>
+    <t>Il rapporto evidenzia barriere protettive, sistemi anticaduta e istruzioni di lavoro illustrate più chiare presso Gamma Chimica. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Può essere migliorato</t>
+  </si>
+  <si>
+    <t>A casa, quale abitudine supporta meglio l'SDG 3?</t>
+  </si>
+  <si>
+    <t>Conservare in modo sicuro prodotti chimici e medicinali</t>
+  </si>
+  <si>
+    <t>Ignorare le etichette di avvertimento</t>
+  </si>
+  <si>
+    <t>Lasciare i pericoli a qualcun altro</t>
+  </si>
+  <si>
+    <t>Mescolare prodotti per la pulizia per renderli più forti</t>
+  </si>
+  <si>
+    <t>Una conservazione sicura previene gli incidenti e protegge le persone a casa. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale scelta nella vita privata contribuisce al benessere?</t>
+  </si>
+  <si>
+    <t>Non chiedere mai aiuto</t>
+  </si>
+  <si>
+    <t>Movimento regolare e riposo adeguato</t>
+  </si>
+  <si>
+    <t>Saltare sempre le pause</t>
+  </si>
+  <si>
+    <t>Ignorare i segnali di stress</t>
+  </si>
+  <si>
+    <t>L'attività fisica, il riposo e la richiesta di sostegno contribuiscono al benessere. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,7 +1332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -334,11 +1346,120 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="35">
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -349,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -365,6 +1490,101 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="Column8"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="14"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -656,7 +1876,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -667,7 +1887,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +1919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +1951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -763,7 +1983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -795,7 +2015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -827,7 +2047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -859,7 +2079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -891,7 +2111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -923,7 +2143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -955,7 +2175,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -987,7 +2207,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1021,6 +2241,1876 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" t="s">
+        <v>385</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1037,16 +4127,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -1210,14 +4290,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFEA699-F64F-49D5-8C93-113698B787A5}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F6FBA2-46D2-433A-ABF4-C4D3CD302A3A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="540" yWindow="1140" windowWidth="28770" windowHeight="15570" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="540" yWindow="540" windowWidth="28770" windowHeight="15570" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
     <sheet name="NL" sheetId="2" r:id="rId2"/>
     <sheet name="FR" sheetId="3" r:id="rId3"/>
-    <sheet name="SP" sheetId="4" r:id="rId4"/>
-    <sheet name="IT" sheetId="5" r:id="rId5"/>
-    <sheet name="GE" sheetId="6" r:id="rId6"/>
+    <sheet name="PL" sheetId="7" r:id="rId4"/>
+    <sheet name="SP" sheetId="4" r:id="rId5"/>
+    <sheet name="IT" sheetId="5" r:id="rId6"/>
+    <sheet name="GE" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="475">
   <si>
     <t>type</t>
   </si>
@@ -1271,13 +1272,208 @@
   </si>
   <si>
     <t>L'attività fisica, il riposo e la richiesta di sostegno contribuiscono al benessere. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Jaka jest główna idea SDG 3 – Dobre zdrowie i jakość życia?</t>
+  </si>
+  <si>
+    <t>Łatwe · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Koncentruje się na zdrowiu i bezpieczeństwie w miejscu pracy.</t>
+  </si>
+  <si>
+    <t>Dotyczy wyłącznie rządów krajowych.</t>
+  </si>
+  <si>
+    <t>Wzywa firmy do ignorowania długoterminowych skutków.</t>
+  </si>
+  <si>
+    <t>Jest jedynie sloganem marketingowym bez praktycznego znaczenia.</t>
+  </si>
+  <si>
+    <t>SDG 3 dotyczy zdrowia i bezpieczeństwa w miejscu pracy oraz przekładania tego celu na konkretne działania. SDG 3 staje się użyteczne, gdy ludzie przekładają ogólny cel na praktyczne decyzje.</t>
+  </si>
+  <si>
+    <t>W porządku</t>
+  </si>
+  <si>
+    <t>Dlaczego SDG 3 jest istotne dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Średnie · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój ma miejsce wyłącznie w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ bezpieczne obchodzenie się z chemikaliami może wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Ponieważ SDG zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Bezpieczne obchodzenie się z chemikaliami jest praktycznym obszarem, w którym firma może coś zmienić. SDG łączą globalne cele z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie jest częstym błędnym przekonaniem na temat SDG 3?</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne codzienne nawyki.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i ograniczać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>Za zdrowie odpowiadają wyłącznie szpitale.</t>
+  </si>
+  <si>
+    <t>SDG 3 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>To błędne przekonanie nadmiernie zawęża zakres SDG i przesłania praktyczne możliwości działania. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu wiedza lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada SDG 3 z teorii na działanie?</t>
+  </si>
+  <si>
+    <t>Postępowanie odwrotnie, gdy nikt nie sprawdza.</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne wdrożenie go.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie sprzyja uczeniu się i prowadzi do wymiernej poprawy. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowań.</t>
+  </si>
+  <si>
+    <t>Co sprawia, że SDG 3 jest wartościowym tematem edukacyjnym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami, które ludzie rozpoznają w pracy i w domu.</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź na każdą sytuację.</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę posiadania wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą organizacyjną.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsza nauka zachodzi wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi im wyborami. SDG najbardziej angażują, gdy są istotne, konkretne i powiązane z rolami poszczególnych osób.</t>
+  </si>
+  <si>
+    <t>Jaką ambicję dotyczącą bezpieczeństwa deklaruje STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Zastąpienie wszystkich szkoleń z zakresu bezpieczeństwa plakatami</t>
+  </si>
+  <si>
+    <t>Zero wypadków związanych z pracą</t>
+  </si>
+  <si>
+    <t>Ograniczanie wypadków wyłącznie w biurach</t>
+  </si>
+  <si>
+    <t>Akceptowanie wypadków, jeśli cele produkcyjne zostaną osiągnięte</t>
+  </si>
+  <si>
+    <t>W raporcie określono ambicję osiągnięcia zerowej liczby wypadków związanych z pracą oraz zerowego szkodliwego wpływu na zdrowie. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Który z raportowanych wyników potwierdza monitorowanie zdrowia w miejscu pracy?</t>
+  </si>
+  <si>
+    <t>Trudne · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Wypadki nie są rejestrowane</t>
+  </si>
+  <si>
+    <t>Tylko kadra kierownicza otrzymuje informacje dotyczące bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy</t>
+  </si>
+  <si>
+    <t>Bezpieczeństwo jest mierzone tylko raz na dziesięć lat</t>
+  </si>
+  <si>
+    <t>W raporcie stwierdzono, że 100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Które działanie Gamma Chimica stanowi praktyczne usprawnienie w zakresie bezpieczeństwa?</t>
+  </si>
+  <si>
+    <t>Ograniczenie komunikacji na temat ryzyka</t>
+  </si>
+  <si>
+    <t>Zaprzestanie zgłaszania zdarzeń potencjalnie wypadkowych</t>
+  </si>
+  <si>
+    <t>Usunięcie wszystkich instrukcji pracy</t>
+  </si>
+  <si>
+    <t>Bariery ochronne i systemy zabezpieczające przed upadkiem</t>
+  </si>
+  <si>
+    <t>W raporcie podkreślono zastosowanie w Gamma Chimica barier ochronnych, zabezpieczeń przed upadkiem oraz bardziej przejrzystych instrukcji pracy opartych na ilustracjach. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Można poprawić</t>
+  </si>
+  <si>
+    <t>Który nawyk w domu najlepiej wspiera SDG 3?</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie chemikaliów i leków</t>
+  </si>
+  <si>
+    <t>Ignorowanie etykiet ostrzegawczych</t>
+  </si>
+  <si>
+    <t>Pozostawianie zagrożeń do usunięcia komuś innemu</t>
+  </si>
+  <si>
+    <t>Mieszanie środków czyszczących, aby zwiększyć ich siłę działania</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie zapobiega wypadkom i chroni ludzi w domu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Który wybór w życiu prywatnym wspiera dobrostan?</t>
+  </si>
+  <si>
+    <t>Nieproszenie nigdy o pomoc</t>
+  </si>
+  <si>
+    <t>Regularna aktywność fizyczna i odpowiedni odpoczynek</t>
+  </si>
+  <si>
+    <t>Ciągłe pomijanie przerw</t>
+  </si>
+  <si>
+    <t>Ignorowanie sygnałów stresu</t>
+  </si>
+  <si>
+    <t>Aktywność fizyczna, odpoczynek i proszenie o wsparcie przyczyniają się do dobrostanu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1301,8 +1497,27 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1319,8 +1534,14 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1328,11 +1549,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1349,11 +1599,366 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1500,15 +2105,15 @@
   <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="42"/>
     <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="38"/>
     <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="Column8"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1519,72 +2124,91 @@
   <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="49"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="45"/>
     <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0">
-  <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0">
-  <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11">
   <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
-    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="17"/>
     <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2996,6 +3620,380 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="56.36328125" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="H3" s="9">
+        <v>2</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H4" s="6">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="H5" s="9">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="H9" s="9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3369,7 +4367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3743,7 +4741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4118,12 +5116,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4291,19 +5290,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4327,11 +5327,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F6FBA2-46D2-433A-ABF4-C4D3CD302A3A}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{014F7BFA-439F-41AA-84D3-AB9FF27A7253}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="540" yWindow="540" windowWidth="28770" windowHeight="15570" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="465">
   <si>
     <t>type</t>
   </si>
@@ -465,36 +465,6 @@
   </si>
   <si>
     <t>Lichaamsbeweging, rust en om steun vragen dragen bij aan welzijn. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
-  </si>
-  <si>
-    <t>Column6</t>
-  </si>
-  <si>
-    <t>Column7</t>
-  </si>
-  <si>
-    <t>Column8</t>
-  </si>
-  <si>
-    <t>Column9</t>
-  </si>
-  <si>
-    <t>Column10</t>
   </si>
   <si>
     <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
@@ -1599,7 +1569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1608,7 +1578,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1617,7 +1587,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1630,7 +1600,167 @@
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="51">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1825,81 +1955,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1938,13 +1993,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -1960,109 +2008,55 @@
       </border>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2075,10 +2069,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2101,19 +2091,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="Column8"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2124,34 +2114,34 @@
   <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="24"/>
     <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
   <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2162,15 +2152,15 @@
   <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="17"/>
     <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2181,15 +2171,15 @@
   <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2200,15 +2190,15 @@
   <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
-    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2500,7 +2490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2511,7 +2501,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2543,7 +2533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2575,7 +2565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2607,7 +2597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2639,7 +2629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2671,7 +2661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2703,7 +2693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2735,7 +2725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2767,7 +2757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2799,7 +2789,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2831,7 +2821,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2874,50 +2864,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2949,7 +2939,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2981,7 +2971,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3013,7 +3003,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3045,7 +3035,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3077,7 +3067,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3109,7 +3099,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3141,7 +3131,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3173,7 +3163,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3205,7 +3195,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3248,18 +3238,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3291,324 +3281,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>232</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>277</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3622,18 +3612,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="34.54296875" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="56.36328125" customWidth="1"/>
-    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="34.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="56.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3665,324 +3655,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="H2" s="6">
         <v>1</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="J3" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>427</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="H4" s="6">
         <v>3</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="H5" s="9">
         <v>4</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H7" s="9">
         <v>2</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="H8" s="6">
         <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>450</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>460</v>
       </c>
       <c r="H9" s="9">
         <v>4</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="H10" s="6">
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>472</v>
-      </c>
       <c r="G11" s="13" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="H11" s="12">
         <v>2</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -3996,18 +3986,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4039,324 +4029,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>297</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>330</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C10" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>342</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -4370,18 +4360,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4413,324 +4403,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>362</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>395</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C11" t="s">
-        <v>346</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>407</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -4744,18 +4734,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4787,324 +4777,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="H4" s="2">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="H9" s="2">
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5116,13 +5106,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5290,20 +5279,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5327,9 +5315,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A0C93D3-8B28-4AC3-A0F9-C26694C97848}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D53E76-6D31-4E43-825B-9B71E914DE4E}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="113">
   <si>
     <t>type</t>
   </si>
@@ -77,48 +77,9 @@
     <t>single</t>
   </si>
   <si>
-    <t>What is the main idea behind SDG 3 – Good Health and Well-Being?</t>
-  </si>
-  <si>
-    <t>Easy · Single choice</t>
-  </si>
-  <si>
-    <t>It focuses on workplace health and safety.</t>
-  </si>
-  <si>
-    <t>It only applies to national governments.</t>
-  </si>
-  <si>
-    <t>It asks companies to ignore long-term impacts.</t>
-  </si>
-  <si>
-    <t>It is only a marketing slogan with no practical meaning.</t>
-  </si>
-  <si>
-    <t>SDG 3 is about workplace health and safety and turning that goal into practical action. SDG 3 becomes useful when people translate the broad goal into practical decisions.</t>
-  </si>
-  <si>
     <t>Okay</t>
   </si>
   <si>
-    <t>What is STOCKMEIER’s stated ambition related to safety?</t>
-  </si>
-  <si>
-    <t>Replacing all safety training with posters</t>
-  </si>
-  <si>
-    <t>Zero work-related accidents</t>
-  </si>
-  <si>
-    <t>Only reducing accidents in offices</t>
-  </si>
-  <si>
-    <t>Accepting accidents if production targets are met</t>
-  </si>
-  <si>
-    <t>The report states an ambition for zero work-related accidents and zero harmful effects on health. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
-  </si>
-  <si>
     <t>Wat is het belangrijkste idee achter SDG 3 – Goede gezondheid en welzijn?</t>
   </si>
   <si>
@@ -161,45 +122,6 @@
     <t>Het rapport vermeldt de ambitie van nul werkgerelateerde ongevallen en nul schadelijke gevolgen voor de gezondheid. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
   </si>
   <si>
-    <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
-  </si>
-  <si>
-    <t>Leicht · Einfachauswahl</t>
-  </si>
-  <si>
-    <t>Es konzentriert sich auf Gesundheit und Sicherheit am Arbeitsplatz.</t>
-  </si>
-  <si>
-    <t>Es gilt nur für nationale Regierungen.</t>
-  </si>
-  <si>
-    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
-  </si>
-  <si>
-    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
-  </si>
-  <si>
-    <t>Bei SDG 3 geht es um Gesundheit und Sicherheit am Arbeitsplatz und darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 3 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
-  </si>
-  <si>
-    <t>Welches Ziel hat STOCKMEIER in Bezug auf Sicherheit formuliert?</t>
-  </si>
-  <si>
-    <t>Alle Sicherheitsschulungen durch Plakate ersetzen</t>
-  </si>
-  <si>
-    <t>Null arbeitsbedingte Unfälle</t>
-  </si>
-  <si>
-    <t>Nur Unfälle in Büros reduzieren</t>
-  </si>
-  <si>
-    <t>Unfälle akzeptieren, wenn Produktionsziele erreicht werden</t>
-  </si>
-  <si>
-    <t>Der Bericht nennt das Ziel von null arbeitsbedingten Unfällen und null gesundheitsschädlichen Auswirkungen. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
-  </si>
-  <si>
     <t>Quelle est l'idée principale de l'ODD 3 – Bonne santé et bien-être ?</t>
   </si>
   <si>
@@ -366,13 +288,106 @@
   </si>
   <si>
     <t>W raporcie określono ambicję osiągnięcia zerowej liczby wypadków związanych z pracą oraz zerowego szkodliwego wpływu na zdrowie. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>What does sustainability in everyday work mean most of all?</t>
+  </si>
+  <si>
+    <t>Single choice</t>
+  </si>
+  <si>
+    <t>Only large projects matter, not small daily decisions.</t>
+  </si>
+  <si>
+    <t>Sustainability is an ongoing process that we can support every day.</t>
+  </si>
+  <si>
+    <t>Sustainability only concerns environmental departments and managers.</t>
+  </si>
+  <si>
+    <t>Sustainability is a topic for later, not for today's work.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>The report describes sustainability as a daily path, not a one-time goal.</t>
+  </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>Which goals fit the “Zero in Focus” idea?</t>
+  </si>
+  <si>
+    <t>Multiple choice</t>
+  </si>
+  <si>
+    <t>Zero CO₂ emissions</t>
+  </si>
+  <si>
+    <t>Zero accidents at work</t>
+  </si>
+  <si>
+    <t>Zero tolerance for unethical behaviour</t>
+  </si>
+  <si>
+    <t>Zero training</t>
+  </si>
+  <si>
+    <t>0,1,2</t>
+  </si>
+  <si>
+    <t>The idea combines climate, safety and integrity. Training is not a “Zero” goal.</t>
+  </si>
+  <si>
+    <t>Was bedeutet Nachhaltigkeit im Arbeitsalltag vor allem?</t>
+  </si>
+  <si>
+    <t>Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Nur große Projekte zählen, nicht kleine tägliche Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Nachhaltigkeit ist ein fortlaufender Prozess, den wir jeden Tag unterstützen können.</t>
+  </si>
+  <si>
+    <t>Nachhaltigkeit betrifft nur Umweltabteilungen und Führungskräfte.</t>
+  </si>
+  <si>
+    <t>Nachhaltigkeit ist ein Thema für später, nicht für die heutige Arbeit.</t>
+  </si>
+  <si>
+    <t>Der Bericht beschreibt Nachhaltigkeit als einen täglichen Weg und nicht als einmaliges Ziel.</t>
+  </si>
+  <si>
+    <t>Welche Ziele passen zur Idee „Zero in Focus“?</t>
+  </si>
+  <si>
+    <t>Mehrfachauswahl</t>
+  </si>
+  <si>
+    <t>Null CO₂-Emissionen</t>
+  </si>
+  <si>
+    <t>Null Arbeitsunfälle</t>
+  </si>
+  <si>
+    <t>Null Toleranz gegenüber unethischem Verhalten</t>
+  </si>
+  <si>
+    <t>Null Schulungen</t>
+  </si>
+  <si>
+    <t>Die Idee verbindet Klima, Sicherheit und Integrität. Schulungen sind kein „Zero“-Ziel.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,16 +399,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -440,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -468,11 +473,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8D8D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -480,58 +494,268 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
+  <dxfs count="63">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FFD8D8D4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -969,6 +1193,9 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -986,15 +1213,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J3">
   <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation" dataDxfId="9"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1002,19 +1229,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:J3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="60"/>
     <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="56"/>
     <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1025,34 +1252,34 @@
   <autoFilter ref="A1:J3" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="53"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="49"/>
     <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <autoFilter ref="A1:J3" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1063,15 +1290,15 @@
   <autoFilter ref="A1:J3" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="31"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="27"/>
     <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1082,15 +1309,15 @@
   <autoFilter ref="A1:J3" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="24"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="20"/>
     <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1100,16 +1327,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J3">
   <autoFilter ref="A1:J3" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
+    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1445,67 +1672,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
+      <c r="A3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1566,64 +1793,64 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>25</v>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>32</v>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>33</v>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>32</v>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1684,64 +1911,64 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>52</v>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>57</v>
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>59</v>
+      <c r="I2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>60</v>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>64</v>
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>59</v>
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1767,99 +1994,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="B2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="4">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>101</v>
+      <c r="I2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="7">
         <v>2</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>101</v>
+      <c r="I3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1920,64 +2147,64 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>66</v>
+      <c r="B2" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>73</v>
+      <c r="I2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>74</v>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>78</v>
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>73</v>
+      <c r="I3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2038,64 +2265,64 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>80</v>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>85</v>
+        <v>55</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>87</v>
+      <c r="I2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>88</v>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>87</v>
+      <c r="I3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2152,68 +2379,68 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>45</v>
+      <c r="B2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>105</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>51</v>
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2225,16 +2452,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -2398,6 +2615,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2408,16 +2635,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2435,6 +2652,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
   <ds:schemaRefs>

--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D53E76-6D31-4E43-825B-9B71E914DE4E}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{014F7BFA-439F-41AA-84D3-AB9FF27A7253}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="465">
   <si>
     <t>type</t>
   </si>
@@ -77,9 +77,201 @@
     <t>single</t>
   </si>
   <si>
+    <t>What is the main idea behind SDG 3 – Good Health and Well-Being?</t>
+  </si>
+  <si>
+    <t>Easy · Single choice</t>
+  </si>
+  <si>
+    <t>It focuses on workplace health and safety.</t>
+  </si>
+  <si>
+    <t>It only applies to national governments.</t>
+  </si>
+  <si>
+    <t>It asks companies to ignore long-term impacts.</t>
+  </si>
+  <si>
+    <t>It is only a marketing slogan with no practical meaning.</t>
+  </si>
+  <si>
+    <t>SDG 3 is about workplace health and safety and turning that goal into practical action. SDG 3 becomes useful when people translate the broad goal into practical decisions.</t>
+  </si>
+  <si>
     <t>Okay</t>
   </si>
   <si>
+    <t>Why is SDG 3 relevant for a chemical distribution and production company?</t>
+  </si>
+  <si>
+    <t>Medium · Single choice</t>
+  </si>
+  <si>
+    <t>Because sustainability only belongs in annual reports.</t>
+  </si>
+  <si>
+    <t>Because safe handling of chemicals can influence sustainability performance.</t>
+  </si>
+  <si>
+    <t>Because the SDGs replace all legal requirements.</t>
+  </si>
+  <si>
+    <t>Because chemicals have no link with sustainability.</t>
+  </si>
+  <si>
+    <t>Safe handling of chemicals are practical areas where a company can make a difference. The SDGs connect global goals to daily operational choices.</t>
+  </si>
+  <si>
+    <t>Which statement is a common misunderstanding about SDG 3?</t>
+  </si>
+  <si>
+    <t>Employees can contribute through small habits.</t>
+  </si>
+  <si>
+    <t>Companies can measure and improve relevant impacts.</t>
+  </si>
+  <si>
+    <t>Only hospitals are responsible for health.</t>
+  </si>
+  <si>
+    <t>SDG 3 can be linked to daily decisions.</t>
+  </si>
+  <si>
+    <t>This is the misconception: it makes the SDG too narrow and hides practical opportunities. A good quiz question often challenges a misconception, because that makes the learning memorable.</t>
+  </si>
+  <si>
+    <t>Which behaviour best turns SDG 3 from theory into action?</t>
+  </si>
+  <si>
+    <t>Doing the opposite when nobody is checking.</t>
+  </si>
+  <si>
+    <t>Talking about sustainability but changing nothing.</t>
+  </si>
+  <si>
+    <t>Waiting until someone else fixes everything.</t>
+  </si>
+  <si>
+    <t>Choosing a concrete improvement and following through.</t>
+  </si>
+  <si>
+    <t>Concrete action creates learning and measurable improvement. Sustainability awareness should lead to practical behaviour change.</t>
+  </si>
+  <si>
+    <t>What makes SDG 3 a useful learning topic for employees?</t>
+  </si>
+  <si>
+    <t>It links global challenges to choices people recognise at work and at home.</t>
+  </si>
+  <si>
+    <t>It gives one perfect answer for every situation.</t>
+  </si>
+  <si>
+    <t>It removes the need for expert knowledge.</t>
+  </si>
+  <si>
+    <t>It is unrelated to company culture.</t>
+  </si>
+  <si>
+    <t>The strongest learning happens when people see the link between global goals and familiar choices. The SDGs are most engaging when they feel relevant, concrete and connected to people’s roles.</t>
+  </si>
+  <si>
+    <t>What is STOCKMEIER’s stated ambition related to safety?</t>
+  </si>
+  <si>
+    <t>Replacing all safety training with posters</t>
+  </si>
+  <si>
+    <t>Zero work-related accidents</t>
+  </si>
+  <si>
+    <t>Only reducing accidents in offices</t>
+  </si>
+  <si>
+    <t>Accepting accidents if production targets are met</t>
+  </si>
+  <si>
+    <t>The report states an ambition for zero work-related accidents and zero harmful effects on health. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Which reported result supports occupational health monitoring?</t>
+  </si>
+  <si>
+    <t>Hard · Single choice</t>
+  </si>
+  <si>
+    <t>Accidents are not recorded</t>
+  </si>
+  <si>
+    <t>Only managers receive safety information</t>
+  </si>
+  <si>
+    <t>100% of people are covered by health and safety management systems</t>
+  </si>
+  <si>
+    <t>Safety is measured only once every ten years</t>
+  </si>
+  <si>
+    <t>The report states that 100% of people are covered by health and safety management systems. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Which Gamma Chimica action is a practical safety improvement?</t>
+  </si>
+  <si>
+    <t>Reducing communication about risk</t>
+  </si>
+  <si>
+    <t>Stopping near-miss reporting</t>
+  </si>
+  <si>
+    <t>Removing all work instructions</t>
+  </si>
+  <si>
+    <t>Protective barriers and fall protection systems</t>
+  </si>
+  <si>
+    <t>The report highlights protective barriers, fall protection and clearer image-based work instructions at Gamma Chimica. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Can be improved</t>
+  </si>
+  <si>
+    <t>At home, which habit best supports SDG 3?</t>
+  </si>
+  <si>
+    <t>Keeping chemicals and medicines safely stored</t>
+  </si>
+  <si>
+    <t>Ignoring warning labels</t>
+  </si>
+  <si>
+    <t>Leaving hazards for someone else</t>
+  </si>
+  <si>
+    <t>Mixing cleaning products to make them stronger</t>
+  </si>
+  <si>
+    <t>Safe storage prevents accidents and protects people at home. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Which private-life choice contributes to well-being?</t>
+  </si>
+  <si>
+    <t>Never asking for help</t>
+  </si>
+  <si>
+    <t>Regular movement and adequate rest</t>
+  </si>
+  <si>
+    <t>Always skipping breaks</t>
+  </si>
+  <si>
+    <t>Ignoring stress signals</t>
+  </si>
+  <si>
+    <t>Physical activity, rest and asking for support contribute to well-being. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
     <t>Wat is het belangrijkste idee achter SDG 3 – Goede gezondheid en welzijn?</t>
   </si>
   <si>
@@ -104,6 +296,81 @@
     <t>Oké</t>
   </si>
   <si>
+    <t>Waarom is SDG 3 relevant voor een bedrijf dat chemische producten distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen in jaarverslagen thuishoort.</t>
+  </si>
+  <si>
+    <t>Omdat het veilig omgaan met chemicaliën de duurzaamheidsprestaties kan beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat chemicaliën geen verband houden met duurzaamheid.</t>
+  </si>
+  <si>
+    <t>Veilig omgaan met chemicaliën is een praktisch gebied waarop een bedrijf verschil kan maken. De SDG's verbinden wereldwijde doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 3?</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen bijdragen door kleine gewoonten.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>Alleen ziekenhuizen zijn verantwoordelijk voor gezondheid.</t>
+  </si>
+  <si>
+    <t>SDG 3 kan worden gekoppeld aan dagelijkse beslissingen.</t>
+  </si>
+  <si>
+    <t>Dit is het misverstand: het maakt de SDG te beperkt en verhult praktische mogelijkheden. Een goede quizvraag stelt vaak een misvatting ter discussie, omdat dit de leerstof beter doet beklijven.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 3 het beste om van theorie naar praktijk?</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die daadwerkelijk uitvoeren.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn van duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Wat maakt SDG 3 een nuttig leerthema voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het koppelt wereldwijde uitdagingen aan keuzes die mensen op het werk en thuis herkennen.</t>
+  </si>
+  <si>
+    <t>Het geeft voor elke situatie één perfect antwoord.</t>
+  </si>
+  <si>
+    <t>Het maakt deskundige kennis overbodig.</t>
+  </si>
+  <si>
+    <t>Het houdt geen verband met de bedrijfscultuur.</t>
+  </si>
+  <si>
+    <t>Mensen leren het meest wanneer ze het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG's zijn het meest aansprekend wanneer ze relevant en concreet aanvoelen en aansluiten bij de rollen van mensen.</t>
+  </si>
+  <si>
     <t>Wat is de uitgesproken ambitie van STOCKMEIER op het gebied van veiligheid?</t>
   </si>
   <si>
@@ -122,6 +389,276 @@
     <t>Het rapport vermeldt de ambitie van nul werkgerelateerde ongevallen en nul schadelijke gevolgen voor de gezondheid. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
   </si>
   <si>
+    <t>Welk gerapporteerd resultaat ondersteunt het toezicht op de gezondheid op het werk?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Ongevallen worden niet geregistreerd</t>
+  </si>
+  <si>
+    <t>Alleen managers ontvangen veiligheidsinformatie</t>
+  </si>
+  <si>
+    <t>100% van de mensen valt onder gezondheids- en veiligheidsmanagementsystemen</t>
+  </si>
+  <si>
+    <t>Veiligheid wordt slechts eens in de tien jaar gemeten</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat 100% van de mensen onder gezondheids- en veiligheidsmanagementsystemen valt. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke actie van Gamma Chimica is een praktische veiligheidsverbetering?</t>
+  </si>
+  <si>
+    <t>Minder communiceren over risico's</t>
+  </si>
+  <si>
+    <t>Stoppen met het melden van bijna-ongevallen</t>
+  </si>
+  <si>
+    <t>Alle werkinstructies verwijderen</t>
+  </si>
+  <si>
+    <t>Beschermende barrières en valbeveiligingssystemen</t>
+  </si>
+  <si>
+    <t>Het rapport belicht beschermende barrières, valbeveiliging en duidelijkere werkinstructies met afbeeldingen bij Gamma Chimica. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Kan worden verbeterd</t>
+  </si>
+  <si>
+    <t>Welke gewoonte thuis ondersteunt SDG 3 het beste?</t>
+  </si>
+  <si>
+    <t>Chemicaliën en medicijnen veilig opbergen</t>
+  </si>
+  <si>
+    <t>Waarschuwingsetiketten negeren</t>
+  </si>
+  <si>
+    <t>Gevaren voor iemand anders laten liggen</t>
+  </si>
+  <si>
+    <t>Schoonmaakmiddelen mengen om ze sterker te maken</t>
+  </si>
+  <si>
+    <t>Veilige opslag voorkomt ongevallen en beschermt mensen thuis. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Welke keuze in het privéleven draagt bij aan welzijn?</t>
+  </si>
+  <si>
+    <t>Nooit om hulp vragen</t>
+  </si>
+  <si>
+    <t>Regelmatig bewegen en voldoende rusten</t>
+  </si>
+  <si>
+    <t>Altijd pauzes overslaan</t>
+  </si>
+  <si>
+    <t>Stresssignalen negeren</t>
+  </si>
+  <si>
+    <t>Lichaamsbeweging, rust en om steun vragen dragen bij aan welzijn. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
+  </si>
+  <si>
+    <t>Leicht · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf Gesundheit und Sicherheit am Arbeitsplatz.</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Bei SDG 3 geht es um Gesundheit und Sicherheit am Arbeitsplatz und darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 3 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 3 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil der sichere Umgang mit Chemikalien die Nachhaltigkeitsleistung beeinflussen kann.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Der sichere Umgang mit Chemikalien ist ein praktischer Bereich, in dem ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 3?</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten einen Beitrag leisten.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>Nur Krankenhäuser sind für Gesundheit verantwortlich.</t>
+  </si>
+  <si>
+    <t>SDG 3 lässt sich mit täglichen Entscheidungen verknüpfen.</t>
+  </si>
+  <si>
+    <t>Das ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Möglichkeiten. Eine gute Quizfrage hinterfragt häufig ein Missverständnis, weil dadurch das Gelernte besser im Gedächtnis bleibt.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 3 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand kontrolliert.</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles in Ordnung bringt.</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln ermöglicht Lernen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu einer praktischen Verhaltensänderung führen.</t>
+  </si>
+  <si>
+    <t>Was macht SDG 3 zu einem nützlichen Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen bei der Arbeit und zu Hause kennen.</t>
+  </si>
+  <si>
+    <t>Es liefert für jede Situation eine einzige perfekte Antwort.</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Es hat keinen Bezug zur Unternehmenskultur.</t>
+  </si>
+  <si>
+    <t>Am meisten lernen Menschen, wenn sie den Zusammenhang zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind besonders ansprechend, wenn sie relevant und konkret wirken und mit den Rollen der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches Ziel hat STOCKMEIER in Bezug auf Sicherheit formuliert?</t>
+  </si>
+  <si>
+    <t>Alle Sicherheitsschulungen durch Plakate ersetzen</t>
+  </si>
+  <si>
+    <t>Null arbeitsbedingte Unfälle</t>
+  </si>
+  <si>
+    <t>Nur Unfälle in Büros reduzieren</t>
+  </si>
+  <si>
+    <t>Unfälle akzeptieren, wenn Produktionsziele erreicht werden</t>
+  </si>
+  <si>
+    <t>Der Bericht nennt das Ziel von null arbeitsbedingten Unfällen und null gesundheitsschädlichen Auswirkungen. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches berichtete Ergebnis unterstützt die Überwachung der Gesundheit am Arbeitsplatz?</t>
+  </si>
+  <si>
+    <t>Schwer · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Unfälle werden nicht erfasst</t>
+  </si>
+  <si>
+    <t>Nur Führungskräfte erhalten Sicherheitsinformationen</t>
+  </si>
+  <si>
+    <t>100 % der Menschen werden von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst</t>
+  </si>
+  <si>
+    <t>Sicherheit wird nur einmal alle zehn Jahre gemessen</t>
+  </si>
+  <si>
+    <t>Der Bericht besagt, dass 100 % der Menschen von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst werden. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Maßnahme von Gamma Chimica ist eine praktische Sicherheitsverbesserung?</t>
+  </si>
+  <si>
+    <t>Weniger über Risiken kommunizieren</t>
+  </si>
+  <si>
+    <t>Die Meldung von Beinaheunfällen einstellen</t>
+  </si>
+  <si>
+    <t>Alle Arbeitsanweisungen entfernen</t>
+  </si>
+  <si>
+    <t>Schutzbarrieren und Absturzsicherungssysteme</t>
+  </si>
+  <si>
+    <t>Der Bericht hebt Schutzbarrieren, Absturzsicherungen und klarere bildgestützte Arbeitsanweisungen bei Gamma Chimica hervor. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Kann verbessert werden</t>
+  </si>
+  <si>
+    <t>Welche Gewohnheit zu Hause unterstützt SDG 3 am besten?</t>
+  </si>
+  <si>
+    <t>Chemikalien und Medikamente sicher aufbewahren</t>
+  </si>
+  <si>
+    <t>Warnhinweise ignorieren</t>
+  </si>
+  <si>
+    <t>Gefahren für jemand anderen liegen lassen</t>
+  </si>
+  <si>
+    <t>Reinigungsmittel mischen, um sie stärker zu machen</t>
+  </si>
+  <si>
+    <t>Eine sichere Aufbewahrung verhindert Unfälle und schützt Menschen zu Hause. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Welche Entscheidung im Privatleben trägt zum Wohlbefinden bei?</t>
+  </si>
+  <si>
+    <t>Nie um Hilfe bitten</t>
+  </si>
+  <si>
+    <t>Regelmäßige Bewegung und ausreichend Erholung</t>
+  </si>
+  <si>
+    <t>Pausen immer auslassen</t>
+  </si>
+  <si>
+    <t>Stresssignale ignorieren</t>
+  </si>
+  <si>
+    <t>Körperliche Aktivität, Erholung und die Bitte um Unterstützung tragen zum Wohlbefinden bei. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
     <t>Quelle est l'idée principale de l'ODD 3 – Bonne santé et bien-être ?</t>
   </si>
   <si>
@@ -146,6 +683,81 @@
     <t>D'accord</t>
   </si>
   <si>
+    <t>Pourquoi l'ODD 3 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité ne concerne que les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que la manipulation sûre des produits chimiques peut influencer la performance en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n'ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>La manipulation sûre des produits chimiques est un domaine concret dans lequel une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante au sujet de l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Les collaborateurs peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>Seuls les hôpitaux sont responsables de la santé.</t>
+  </si>
+  <si>
+    <t>L'ODD 3 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>Voici l'idée fausse : elle réduit trop la portée de l'ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée reçue, car cela rend l'apprentissage mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement permet le mieux de faire passer l'ODD 3 de la théorie à l'action ?</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne vérifie.</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu'un d'autre règle tout.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mener à bien.</t>
+  </si>
+  <si>
+    <t>Une action concrète favorise l'apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Pourquoi l'ODD 3 constitue-t-il un sujet d'apprentissage utile pour les collaborateurs ?</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Il fournit une réponse parfaite pour chaque situation.</t>
+  </si>
+  <si>
+    <t>Il supprime la nécessité de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>Il n'a aucun rapport avec la culture d'entreprise.</t>
+  </si>
+  <si>
+    <t>L'apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et des choix familiers. Les ODD sont plus motivants lorsqu'ils paraissent pertinents, concrets et liés au rôle de chacun.</t>
+  </si>
+  <si>
     <t>Quelle est l'ambition déclarée de STOCKMEIER en matière de sécurité ?</t>
   </si>
   <si>
@@ -164,6 +776,84 @@
     <t>Le rapport énonce une ambition de zéro accident lié au travail et de zéro effet nocif sur la santé. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
   </si>
   <si>
+    <t>Quel résultat communiqué soutient le suivi de la santé au travail ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>Les accidents ne sont pas enregistrés</t>
+  </si>
+  <si>
+    <t>Seuls les responsables reçoivent des informations sur la sécurité</t>
+  </si>
+  <si>
+    <t>100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité</t>
+  </si>
+  <si>
+    <t>La sécurité n'est mesurée qu'une fois tous les dix ans</t>
+  </si>
+  <si>
+    <t>Le rapport indique que 100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quelle action de Gamma Chimica constitue une amélioration concrète de la sécurité ?</t>
+  </si>
+  <si>
+    <t>Réduire la communication sur les risques</t>
+  </si>
+  <si>
+    <t>Cesser de signaler les quasi-accidents</t>
+  </si>
+  <si>
+    <t>Supprimer toutes les instructions de travail</t>
+  </si>
+  <si>
+    <t>Des barrières de protection et des systèmes antichute</t>
+  </si>
+  <si>
+    <t>Le rapport met en avant les barrières de protection, les systèmes antichute et des instructions de travail illustrées plus claires chez Gamma Chimica. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Peut être amélioré</t>
+  </si>
+  <si>
+    <t>À la maison, quelle habitude soutient le mieux l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Ranger les produits chimiques et les médicaments en toute sécurité</t>
+  </si>
+  <si>
+    <t>Ignorer les étiquettes d'avertissement</t>
+  </si>
+  <si>
+    <t>Laisser les dangers à quelqu'un d'autre</t>
+  </si>
+  <si>
+    <t>Mélanger des produits de nettoyage pour les rendre plus puissants</t>
+  </si>
+  <si>
+    <t>Un rangement sûr prévient les accidents et protège les personnes à la maison. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Quel choix dans la vie privée contribue au bien-être ?</t>
+  </si>
+  <si>
+    <t>Ne jamais demander d'aide</t>
+  </si>
+  <si>
+    <t>Bouger régulièrement et se reposer suffisamment</t>
+  </si>
+  <si>
+    <t>Toujours sauter les pauses</t>
+  </si>
+  <si>
+    <t>Ignorer les signes de stress</t>
+  </si>
+  <si>
+    <t>L'activité physique, le repos et le fait de demander du soutien contribuent au bien-être. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
     <t>¿Cuál es la idea principal del ODS 3 – Salud y bienestar?</t>
   </si>
   <si>
@@ -188,6 +878,81 @@
     <t>De acuerdo</t>
   </si>
   <si>
+    <t>¿Por qué es relevante el ODS 3 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Medio · Opción única</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo pertenece a los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque la manipulación segura de productos químicos puede influir en el desempeño en sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>La manipulación segura de productos químicos es un ámbito práctico en el que una empresa puede marcar la diferencia. Los ODS conectan los objetivos globales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido habitual sobre el ODS 3?</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>Solo los hospitales son responsables de la salud.</t>
+  </si>
+  <si>
+    <t>El ODS 3 puede vincularse a las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: limita demasiado el ODS y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar una idea errónea, porque así el aprendizaje resulta memorable.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 3 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está comprobándolo.</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>Esperar hasta que otra persona lo solucione todo.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio de comportamiento práctico.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 3 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>Relaciona los desafíos globales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura empresarial.</t>
+  </si>
+  <si>
+    <t>El aprendizaje es más sólido cuando las personas ven el vínculo entre los objetivos globales y las decisiones conocidas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y conectados con las funciones de las personas.</t>
+  </si>
+  <si>
     <t>¿Cuál es la ambición declarada de STOCKMEIER en relación con la seguridad?</t>
   </si>
   <si>
@@ -206,6 +971,84 @@
     <t>El informe establece la ambición de cero accidentes laborales y cero efectos perjudiciales para la salud. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
   </si>
   <si>
+    <t>¿Qué resultado comunicado respalda el seguimiento de la salud laboral?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>Los accidentes no se registran</t>
+  </si>
+  <si>
+    <t>Solo los directivos reciben información sobre seguridad</t>
+  </si>
+  <si>
+    <t>El 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad</t>
+  </si>
+  <si>
+    <t>La seguridad se mide solo una vez cada diez años</t>
+  </si>
+  <si>
+    <t>El informe indica que el 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué acción de Gamma Chimica supone una mejora práctica de la seguridad?</t>
+  </si>
+  <si>
+    <t>Reducir la comunicación sobre los riesgos</t>
+  </si>
+  <si>
+    <t>Dejar de informar sobre cuasiaccidentes</t>
+  </si>
+  <si>
+    <t>Eliminar todas las instrucciones de trabajo</t>
+  </si>
+  <si>
+    <t>Barreras de protección y sistemas anticaídas</t>
+  </si>
+  <si>
+    <t>El informe destaca las barreras de protección, los sistemas anticaídas y unas instrucciones de trabajo con imágenes más claras en Gamma Chimica. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>Puede mejorarse</t>
+  </si>
+  <si>
+    <t>En casa, ¿qué hábito apoya mejor el ODS 3?</t>
+  </si>
+  <si>
+    <t>Guardar de forma segura los productos químicos y los medicamentos</t>
+  </si>
+  <si>
+    <t>Ignorar las etiquetas de advertencia</t>
+  </si>
+  <si>
+    <t>Dejar los peligros para otra persona</t>
+  </si>
+  <si>
+    <t>Mezclar productos de limpieza para hacerlos más fuertes</t>
+  </si>
+  <si>
+    <t>El almacenamiento seguro evita accidentes y protege a las personas en casa. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Qué elección en la vida privada contribuye al bienestar?</t>
+  </si>
+  <si>
+    <t>No pedir ayuda nunca</t>
+  </si>
+  <si>
+    <t>Actividad física regular y descanso adecuado</t>
+  </si>
+  <si>
+    <t>Saltarse siempre las pausas</t>
+  </si>
+  <si>
+    <t>Ignorar las señales de estrés</t>
+  </si>
+  <si>
+    <t>La actividad física, el descanso y pedir apoyo contribuyen al bienestar. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
     <t>Qual è l'idea principale alla base dell'SDG 3 – Salute e benessere?</t>
   </si>
   <si>
@@ -230,6 +1073,81 @@
     <t>Va bene</t>
   </si>
   <si>
+    <t>Perché l'SDG 3 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Risposta singola</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità riguarda soltanto i rapporti annuali.</t>
+  </si>
+  <si>
+    <t>Perché la manipolazione sicura dei prodotti chimici può influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli SDG sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>La manipolazione sicura dei prodotti chimici è un ambito concreto in cui un'azienda può fare la differenza. Gli SDG collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull'SDG 3?</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>Solo gli ospedali sono responsabili della salute.</t>
+  </si>
+  <si>
+    <t>L'SDG 3 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo l'SDG e nasconde opportunità concrete. Una buona domanda di un quiz spesso mette in discussione un'idea errata, perché rende memorabile l'apprendimento.</t>
+  </si>
+  <si>
+    <t>Quale comportamento trasforma meglio l'SDG 3 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico del comportamento.</t>
+  </si>
+  <si>
+    <t>Cosa rende l'SDG 3 un argomento formativo utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Fornisce una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>Non ha alcun rapporto con la cultura aziendale.</t>
+  </si>
+  <si>
+    <t>L'apprendimento è più efficace quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli SDG sono più coinvolgenti quando appaiono rilevanti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
     <t>Qual è l'ambizione dichiarata di STOCKMEIER in materia di sicurezza?</t>
   </si>
   <si>
@@ -248,6 +1166,84 @@
     <t>Il rapporto dichiara l'ambizione di zero infortuni sul lavoro e zero effetti nocivi sulla salute. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
   </si>
   <si>
+    <t>Quale risultato riportato supporta il monitoraggio della salute sul lavoro?</t>
+  </si>
+  <si>
+    <t>Difficile · Risposta singola</t>
+  </si>
+  <si>
+    <t>Gli incidenti non vengono registrati</t>
+  </si>
+  <si>
+    <t>Solo i dirigenti ricevono informazioni sulla sicurezza</t>
+  </si>
+  <si>
+    <t>Il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza</t>
+  </si>
+  <si>
+    <t>La sicurezza viene misurata soltanto una volta ogni dieci anni</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale azione di Gamma Chimica rappresenta un miglioramento pratico della sicurezza?</t>
+  </si>
+  <si>
+    <t>Ridurre la comunicazione sui rischi</t>
+  </si>
+  <si>
+    <t>Interrompere la segnalazione dei mancati incidenti</t>
+  </si>
+  <si>
+    <t>Rimuovere tutte le istruzioni di lavoro</t>
+  </si>
+  <si>
+    <t>Barriere protettive e sistemi anticaduta</t>
+  </si>
+  <si>
+    <t>Il rapporto evidenzia barriere protettive, sistemi anticaduta e istruzioni di lavoro illustrate più chiare presso Gamma Chimica. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Può essere migliorato</t>
+  </si>
+  <si>
+    <t>A casa, quale abitudine supporta meglio l'SDG 3?</t>
+  </si>
+  <si>
+    <t>Conservare in modo sicuro prodotti chimici e medicinali</t>
+  </si>
+  <si>
+    <t>Ignorare le etichette di avvertimento</t>
+  </si>
+  <si>
+    <t>Lasciare i pericoli a qualcun altro</t>
+  </si>
+  <si>
+    <t>Mescolare prodotti per la pulizia per renderli più forti</t>
+  </si>
+  <si>
+    <t>Una conservazione sicura previene gli incidenti e protegge le persone a casa. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale scelta nella vita privata contribuisce al benessere?</t>
+  </si>
+  <si>
+    <t>Non chiedere mai aiuto</t>
+  </si>
+  <si>
+    <t>Movimento regolare e riposo adeguato</t>
+  </si>
+  <si>
+    <t>Saltare sempre le pause</t>
+  </si>
+  <si>
+    <t>Ignorare i segnali di stress</t>
+  </si>
+  <si>
+    <t>L'attività fisica, il riposo e la richiesta di sostegno contribuiscono al benessere. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
     <t>Jaka jest główna idea SDG 3 – Dobre zdrowie i jakość życia?</t>
   </si>
   <si>
@@ -272,6 +1268,81 @@
     <t>W porządku</t>
   </si>
   <si>
+    <t>Dlaczego SDG 3 jest istotne dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Średnie · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój ma miejsce wyłącznie w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ bezpieczne obchodzenie się z chemikaliami może wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Ponieważ SDG zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Bezpieczne obchodzenie się z chemikaliami jest praktycznym obszarem, w którym firma może coś zmienić. SDG łączą globalne cele z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie jest częstym błędnym przekonaniem na temat SDG 3?</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne codzienne nawyki.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i ograniczać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>Za zdrowie odpowiadają wyłącznie szpitale.</t>
+  </si>
+  <si>
+    <t>SDG 3 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>To błędne przekonanie nadmiernie zawęża zakres SDG i przesłania praktyczne możliwości działania. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu wiedza lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada SDG 3 z teorii na działanie?</t>
+  </si>
+  <si>
+    <t>Postępowanie odwrotnie, gdy nikt nie sprawdza.</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne wdrożenie go.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie sprzyja uczeniu się i prowadzi do wymiernej poprawy. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowań.</t>
+  </si>
+  <si>
+    <t>Co sprawia, że SDG 3 jest wartościowym tematem edukacyjnym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami, które ludzie rozpoznają w pracy i w domu.</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź na każdą sytuację.</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę posiadania wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą organizacyjną.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsza nauka zachodzi wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi im wyborami. SDG najbardziej angażują, gdy są istotne, konkretne i powiązane z rolami poszczególnych osób.</t>
+  </si>
+  <si>
     <t>Jaką ambicję dotyczącą bezpieczeństwa deklaruje STOCKMEIER?</t>
   </si>
   <si>
@@ -290,104 +1361,89 @@
     <t>W raporcie określono ambicję osiągnięcia zerowej liczby wypadków związanych z pracą oraz zerowego szkodliwego wpływu na zdrowie. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
   </si>
   <si>
-    <t>What does sustainability in everyday work mean most of all?</t>
-  </si>
-  <si>
-    <t>Single choice</t>
-  </si>
-  <si>
-    <t>Only large projects matter, not small daily decisions.</t>
-  </si>
-  <si>
-    <t>Sustainability is an ongoing process that we can support every day.</t>
-  </si>
-  <si>
-    <t>Sustainability only concerns environmental departments and managers.</t>
-  </si>
-  <si>
-    <t>Sustainability is a topic for later, not for today's work.</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>The report describes sustainability as a daily path, not a one-time goal.</t>
-  </si>
-  <si>
-    <t>multiple</t>
-  </si>
-  <si>
-    <t>Which goals fit the “Zero in Focus” idea?</t>
-  </si>
-  <si>
-    <t>Multiple choice</t>
-  </si>
-  <si>
-    <t>Zero CO₂ emissions</t>
-  </si>
-  <si>
-    <t>Zero accidents at work</t>
-  </si>
-  <si>
-    <t>Zero tolerance for unethical behaviour</t>
-  </si>
-  <si>
-    <t>Zero training</t>
-  </si>
-  <si>
-    <t>0,1,2</t>
-  </si>
-  <si>
-    <t>The idea combines climate, safety and integrity. Training is not a “Zero” goal.</t>
-  </si>
-  <si>
-    <t>Was bedeutet Nachhaltigkeit im Arbeitsalltag vor allem?</t>
-  </si>
-  <si>
-    <t>Einfachauswahl</t>
-  </si>
-  <si>
-    <t>Nur große Projekte zählen, nicht kleine tägliche Entscheidungen.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein fortlaufender Prozess, den wir jeden Tag unterstützen können.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit betrifft nur Umweltabteilungen und Führungskräfte.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein Thema für später, nicht für die heutige Arbeit.</t>
-  </si>
-  <si>
-    <t>Der Bericht beschreibt Nachhaltigkeit als einen täglichen Weg und nicht als einmaliges Ziel.</t>
-  </si>
-  <si>
-    <t>Welche Ziele passen zur Idee „Zero in Focus“?</t>
-  </si>
-  <si>
-    <t>Mehrfachauswahl</t>
-  </si>
-  <si>
-    <t>Null CO₂-Emissionen</t>
-  </si>
-  <si>
-    <t>Null Arbeitsunfälle</t>
-  </si>
-  <si>
-    <t>Null Toleranz gegenüber unethischem Verhalten</t>
-  </si>
-  <si>
-    <t>Null Schulungen</t>
-  </si>
-  <si>
-    <t>Die Idee verbindet Klima, Sicherheit und Integrität. Schulungen sind kein „Zero“-Ziel.</t>
+    <t>Który z raportowanych wyników potwierdza monitorowanie zdrowia w miejscu pracy?</t>
+  </si>
+  <si>
+    <t>Trudne · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Wypadki nie są rejestrowane</t>
+  </si>
+  <si>
+    <t>Tylko kadra kierownicza otrzymuje informacje dotyczące bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy</t>
+  </si>
+  <si>
+    <t>Bezpieczeństwo jest mierzone tylko raz na dziesięć lat</t>
+  </si>
+  <si>
+    <t>W raporcie stwierdzono, że 100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Które działanie Gamma Chimica stanowi praktyczne usprawnienie w zakresie bezpieczeństwa?</t>
+  </si>
+  <si>
+    <t>Ograniczenie komunikacji na temat ryzyka</t>
+  </si>
+  <si>
+    <t>Zaprzestanie zgłaszania zdarzeń potencjalnie wypadkowych</t>
+  </si>
+  <si>
+    <t>Usunięcie wszystkich instrukcji pracy</t>
+  </si>
+  <si>
+    <t>Bariery ochronne i systemy zabezpieczające przed upadkiem</t>
+  </si>
+  <si>
+    <t>W raporcie podkreślono zastosowanie w Gamma Chimica barier ochronnych, zabezpieczeń przed upadkiem oraz bardziej przejrzystych instrukcji pracy opartych na ilustracjach. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Można poprawić</t>
+  </si>
+  <si>
+    <t>Który nawyk w domu najlepiej wspiera SDG 3?</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie chemikaliów i leków</t>
+  </si>
+  <si>
+    <t>Ignorowanie etykiet ostrzegawczych</t>
+  </si>
+  <si>
+    <t>Pozostawianie zagrożeń do usunięcia komuś innemu</t>
+  </si>
+  <si>
+    <t>Mieszanie środków czyszczących, aby zwiększyć ich siłę działania</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie zapobiega wypadkom i chroni ludzi w domu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Który wybór w życiu prywatnym wspiera dobrostan?</t>
+  </si>
+  <si>
+    <t>Nieproszenie nigdy o pomoc</t>
+  </si>
+  <si>
+    <t>Regularna aktywność fizyczna i odpowiedni odpoczynek</t>
+  </si>
+  <si>
+    <t>Ciągłe pomijanie przerw</t>
+  </si>
+  <si>
+    <t>Ignorowanie sygnałów stresu</t>
+  </si>
+  <si>
+    <t>Aktywność fizyczna, odpoczynek i proszenie o wsparcie przyczyniają się do dobrostanu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +1455,16 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -476,22 +1542,28 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D8D4"/>
-      </bottom>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -500,262 +1572,121 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="51">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1127,75 +2058,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1210,18 +2072,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J3">
-  <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1229,114 +2091,114 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="61">
-  <autoFilter ref="A1:J3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="35"/>
     <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="31"/>
     <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}" name="Questions_FR" displayName="Questions_FR" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="24"/>
     <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
-  <autoFilter ref="A1:J3" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+  <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="17"/>
     <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J3">
-  <autoFilter ref="A1:J3" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
     <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1627,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1672,67 +2534,323 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>89</v>
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>98</v>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1745,7 +2863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="100" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1793,64 +2911,320 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
+      <c r="B2" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>77</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
+      <c r="B3" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
+      <c r="I3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1863,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -1911,64 +3285,320 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
+      <c r="B2" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>206</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>33</v>
+      <c r="I2" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
+      <c r="B3" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>38</v>
+        <v>214</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>33</v>
+      <c r="I3" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -1981,7 +3611,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -1994,99 +3624,355 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="H2" s="6">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="I2" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>75</v>
+      <c r="I3" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H4" s="6">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="H5" s="9">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="H9" s="9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +3985,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -2147,64 +4033,320 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>40</v>
+      <c r="B2" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>271</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>47</v>
+      <c r="I2" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>48</v>
+      <c r="B3" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>279</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>47</v>
+      <c r="I3" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -2217,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -2265,64 +4407,320 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>54</v>
+      <c r="B2" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>336</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>62</v>
+      <c r="B3" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>344</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>61</v>
+      <c r="I3" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -2335,7 +4733,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -2379,68 +4777,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>105</v>
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>112</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2452,6 +5106,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -2615,7 +5278,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
@@ -2625,16 +5288,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2652,7 +5314,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2660,12 +5322,4 @@
     <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D53E76-6D31-4E43-825B-9B71E914DE4E}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E1F90F-679A-4B57-A7C5-A373B94A5194}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="475">
   <si>
     <t>type</t>
   </si>
@@ -77,9 +77,186 @@
     <t>single</t>
   </si>
   <si>
+    <t>What is the main idea behind SDG 3 – Good Health and Well-Being?</t>
+  </si>
+  <si>
+    <t>Easy · Single choice</t>
+  </si>
+  <si>
+    <t>It focuses on workplace health and safety.</t>
+  </si>
+  <si>
+    <t>It only applies to national governments.</t>
+  </si>
+  <si>
+    <t>It asks companies to ignore long-term impacts.</t>
+  </si>
+  <si>
+    <t>It is only a marketing slogan with no practical meaning.</t>
+  </si>
+  <si>
+    <t>SDG 3 is about workplace health and safety and turning that goal into practical action. SDG 3 becomes useful when people translate the broad goal into practical decisions.</t>
+  </si>
+  <si>
     <t>Okay</t>
   </si>
   <si>
+    <t>Medium · Single choice</t>
+  </si>
+  <si>
+    <t>Because sustainability only belongs in annual reports.</t>
+  </si>
+  <si>
+    <t>Because safe handling of chemicals can influence sustainability performance.</t>
+  </si>
+  <si>
+    <t>Because the SDGs replace all legal requirements.</t>
+  </si>
+  <si>
+    <t>Because chemicals have no link with sustainability.</t>
+  </si>
+  <si>
+    <t>Safe handling of chemicals are practical areas where a company can make a difference. The SDGs connect global goals to daily operational choices.</t>
+  </si>
+  <si>
+    <t>Employees can contribute through small habits.</t>
+  </si>
+  <si>
+    <t>Companies can measure and improve relevant impacts.</t>
+  </si>
+  <si>
+    <t>Only hospitals are responsible for health.</t>
+  </si>
+  <si>
+    <t>SDG 3 can be linked to daily decisions.</t>
+  </si>
+  <si>
+    <t>This is the misconception: it makes the SDG too narrow and hides practical opportunities. A good quiz question often challenges a misconception, because that makes the learning memorable.</t>
+  </si>
+  <si>
+    <t>Doing the opposite when nobody is checking.</t>
+  </si>
+  <si>
+    <t>Talking about sustainability but changing nothing.</t>
+  </si>
+  <si>
+    <t>Waiting until someone else fixes everything.</t>
+  </si>
+  <si>
+    <t>Choosing a concrete improvement and following through.</t>
+  </si>
+  <si>
+    <t>Concrete action creates learning and measurable improvement. Sustainability awareness should lead to practical behaviour change.</t>
+  </si>
+  <si>
+    <t>It links global challenges to choices people recognise at work and at home.</t>
+  </si>
+  <si>
+    <t>It gives one perfect answer for every situation.</t>
+  </si>
+  <si>
+    <t>It removes the need for expert knowledge.</t>
+  </si>
+  <si>
+    <t>It is unrelated to company culture.</t>
+  </si>
+  <si>
+    <t>The strongest learning happens when people see the link between global goals and familiar choices. The SDGs are most engaging when they feel relevant, concrete and connected to people’s roles.</t>
+  </si>
+  <si>
+    <t>What is STOCKMEIER’s stated ambition related to safety?</t>
+  </si>
+  <si>
+    <t>Replacing all safety training with posters</t>
+  </si>
+  <si>
+    <t>Zero work-related accidents</t>
+  </si>
+  <si>
+    <t>Only reducing accidents in offices</t>
+  </si>
+  <si>
+    <t>Accepting accidents if production targets are met</t>
+  </si>
+  <si>
+    <t>The report states an ambition for zero work-related accidents and zero harmful effects on health. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Which reported result supports occupational health monitoring?</t>
+  </si>
+  <si>
+    <t>Hard · Single choice</t>
+  </si>
+  <si>
+    <t>Accidents are not recorded</t>
+  </si>
+  <si>
+    <t>Only managers receive safety information</t>
+  </si>
+  <si>
+    <t>100% of people are covered by health and safety management systems</t>
+  </si>
+  <si>
+    <t>Safety is measured only once every ten years</t>
+  </si>
+  <si>
+    <t>The report states that 100% of people are covered by health and safety management systems. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Which Gamma Chimica action is a practical safety improvement?</t>
+  </si>
+  <si>
+    <t>Reducing communication about risk</t>
+  </si>
+  <si>
+    <t>Stopping near-miss reporting</t>
+  </si>
+  <si>
+    <t>Removing all work instructions</t>
+  </si>
+  <si>
+    <t>Protective barriers and fall protection systems</t>
+  </si>
+  <si>
+    <t>The report highlights protective barriers, fall protection and clearer image-based work instructions at Gamma Chimica. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
+  </si>
+  <si>
+    <t>Can be improved</t>
+  </si>
+  <si>
+    <t>Keeping chemicals and medicines safely stored</t>
+  </si>
+  <si>
+    <t>Ignoring warning labels</t>
+  </si>
+  <si>
+    <t>Leaving hazards for someone else</t>
+  </si>
+  <si>
+    <t>Mixing cleaning products to make them stronger</t>
+  </si>
+  <si>
+    <t>Safe storage prevents accidents and protects people at home. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Which private-life choice contributes to well-being?</t>
+  </si>
+  <si>
+    <t>Never asking for help</t>
+  </si>
+  <si>
+    <t>Regular movement and adequate rest</t>
+  </si>
+  <si>
+    <t>Always skipping breaks</t>
+  </si>
+  <si>
+    <t>Ignoring stress signals</t>
+  </si>
+  <si>
+    <t>Physical activity, rest and asking for support contribute to well-being. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
     <t>Wat is het belangrijkste idee achter SDG 3 – Goede gezondheid en welzijn?</t>
   </si>
   <si>
@@ -104,6 +281,81 @@
     <t>Oké</t>
   </si>
   <si>
+    <t>Waarom is SDG 3 relevant voor een bedrijf dat chemische producten distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen in jaarverslagen thuishoort.</t>
+  </si>
+  <si>
+    <t>Omdat het veilig omgaan met chemicaliën de duurzaamheidsprestaties kan beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat chemicaliën geen verband houden met duurzaamheid.</t>
+  </si>
+  <si>
+    <t>Veilig omgaan met chemicaliën is een praktisch gebied waarop een bedrijf verschil kan maken. De SDG's verbinden wereldwijde doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 3?</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen bijdragen door kleine gewoonten.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>Alleen ziekenhuizen zijn verantwoordelijk voor gezondheid.</t>
+  </si>
+  <si>
+    <t>SDG 3 kan worden gekoppeld aan dagelijkse beslissingen.</t>
+  </si>
+  <si>
+    <t>Dit is het misverstand: het maakt de SDG te beperkt en verhult praktische mogelijkheden. Een goede quizvraag stelt vaak een misvatting ter discussie, omdat dit de leerstof beter doet beklijven.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 3 het beste om van theorie naar praktijk?</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die daadwerkelijk uitvoeren.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn van duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Wat maakt SDG 3 een nuttig leerthema voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het koppelt wereldwijde uitdagingen aan keuzes die mensen op het werk en thuis herkennen.</t>
+  </si>
+  <si>
+    <t>Het geeft voor elke situatie één perfect antwoord.</t>
+  </si>
+  <si>
+    <t>Het maakt deskundige kennis overbodig.</t>
+  </si>
+  <si>
+    <t>Het houdt geen verband met de bedrijfscultuur.</t>
+  </si>
+  <si>
+    <t>Mensen leren het meest wanneer ze het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG's zijn het meest aansprekend wanneer ze relevant en concreet aanvoelen en aansluiten bij de rollen van mensen.</t>
+  </si>
+  <si>
     <t>Wat is de uitgesproken ambitie van STOCKMEIER op het gebied van veiligheid?</t>
   </si>
   <si>
@@ -122,6 +374,306 @@
     <t>Het rapport vermeldt de ambitie van nul werkgerelateerde ongevallen en nul schadelijke gevolgen voor de gezondheid. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
   </si>
   <si>
+    <t>Welk gerapporteerd resultaat ondersteunt het toezicht op de gezondheid op het werk?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Ongevallen worden niet geregistreerd</t>
+  </si>
+  <si>
+    <t>Alleen managers ontvangen veiligheidsinformatie</t>
+  </si>
+  <si>
+    <t>100% van de mensen valt onder gezondheids- en veiligheidsmanagementsystemen</t>
+  </si>
+  <si>
+    <t>Veiligheid wordt slechts eens in de tien jaar gemeten</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat 100% van de mensen onder gezondheids- en veiligheidsmanagementsystemen valt. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke actie van Gamma Chimica is een praktische veiligheidsverbetering?</t>
+  </si>
+  <si>
+    <t>Minder communiceren over risico's</t>
+  </si>
+  <si>
+    <t>Stoppen met het melden van bijna-ongevallen</t>
+  </si>
+  <si>
+    <t>Alle werkinstructies verwijderen</t>
+  </si>
+  <si>
+    <t>Beschermende barrières en valbeveiligingssystemen</t>
+  </si>
+  <si>
+    <t>Het rapport belicht beschermende barrières, valbeveiliging en duidelijkere werkinstructies met afbeeldingen bij Gamma Chimica. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Kan worden verbeterd</t>
+  </si>
+  <si>
+    <t>Welke gewoonte thuis ondersteunt SDG 3 het beste?</t>
+  </si>
+  <si>
+    <t>Chemicaliën en medicijnen veilig opbergen</t>
+  </si>
+  <si>
+    <t>Waarschuwingsetiketten negeren</t>
+  </si>
+  <si>
+    <t>Gevaren voor iemand anders laten liggen</t>
+  </si>
+  <si>
+    <t>Schoonmaakmiddelen mengen om ze sterker te maken</t>
+  </si>
+  <si>
+    <t>Veilige opslag voorkomt ongevallen en beschermt mensen thuis. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Welke keuze in het privéleven draagt bij aan welzijn?</t>
+  </si>
+  <si>
+    <t>Nooit om hulp vragen</t>
+  </si>
+  <si>
+    <t>Regelmatig bewegen en voldoende rusten</t>
+  </si>
+  <si>
+    <t>Altijd pauzes overslaan</t>
+  </si>
+  <si>
+    <t>Stresssignalen negeren</t>
+  </si>
+  <si>
+    <t>Lichaamsbeweging, rust en om steun vragen dragen bij aan welzijn. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
+    <t>Column8</t>
+  </si>
+  <si>
+    <t>Column9</t>
+  </si>
+  <si>
+    <t>Column10</t>
+  </si>
+  <si>
+    <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
+  </si>
+  <si>
+    <t>Leicht · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf Gesundheit und Sicherheit am Arbeitsplatz.</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Bei SDG 3 geht es um Gesundheit und Sicherheit am Arbeitsplatz und darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 3 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 3 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil der sichere Umgang mit Chemikalien die Nachhaltigkeitsleistung beeinflussen kann.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Der sichere Umgang mit Chemikalien ist ein praktischer Bereich, in dem ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 3?</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten einen Beitrag leisten.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>Nur Krankenhäuser sind für Gesundheit verantwortlich.</t>
+  </si>
+  <si>
+    <t>SDG 3 lässt sich mit täglichen Entscheidungen verknüpfen.</t>
+  </si>
+  <si>
+    <t>Das ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Möglichkeiten. Eine gute Quizfrage hinterfragt häufig ein Missverständnis, weil dadurch das Gelernte besser im Gedächtnis bleibt.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 3 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand kontrolliert.</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles in Ordnung bringt.</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln ermöglicht Lernen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu einer praktischen Verhaltensänderung führen.</t>
+  </si>
+  <si>
+    <t>Was macht SDG 3 zu einem nützlichen Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen bei der Arbeit und zu Hause kennen.</t>
+  </si>
+  <si>
+    <t>Es liefert für jede Situation eine einzige perfekte Antwort.</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Es hat keinen Bezug zur Unternehmenskultur.</t>
+  </si>
+  <si>
+    <t>Am meisten lernen Menschen, wenn sie den Zusammenhang zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind besonders ansprechend, wenn sie relevant und konkret wirken und mit den Rollen der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches Ziel hat STOCKMEIER in Bezug auf Sicherheit formuliert?</t>
+  </si>
+  <si>
+    <t>Alle Sicherheitsschulungen durch Plakate ersetzen</t>
+  </si>
+  <si>
+    <t>Null arbeitsbedingte Unfälle</t>
+  </si>
+  <si>
+    <t>Nur Unfälle in Büros reduzieren</t>
+  </si>
+  <si>
+    <t>Unfälle akzeptieren, wenn Produktionsziele erreicht werden</t>
+  </si>
+  <si>
+    <t>Der Bericht nennt das Ziel von null arbeitsbedingten Unfällen und null gesundheitsschädlichen Auswirkungen. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches berichtete Ergebnis unterstützt die Überwachung der Gesundheit am Arbeitsplatz?</t>
+  </si>
+  <si>
+    <t>Schwer · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Unfälle werden nicht erfasst</t>
+  </si>
+  <si>
+    <t>Nur Führungskräfte erhalten Sicherheitsinformationen</t>
+  </si>
+  <si>
+    <t>100 % der Menschen werden von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst</t>
+  </si>
+  <si>
+    <t>Sicherheit wird nur einmal alle zehn Jahre gemessen</t>
+  </si>
+  <si>
+    <t>Der Bericht besagt, dass 100 % der Menschen von Arbeits- und Gesundheitsschutzmanagementsystemen erfasst werden. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Maßnahme von Gamma Chimica ist eine praktische Sicherheitsverbesserung?</t>
+  </si>
+  <si>
+    <t>Weniger über Risiken kommunizieren</t>
+  </si>
+  <si>
+    <t>Die Meldung von Beinaheunfällen einstellen</t>
+  </si>
+  <si>
+    <t>Alle Arbeitsanweisungen entfernen</t>
+  </si>
+  <si>
+    <t>Schutzbarrieren und Absturzsicherungssysteme</t>
+  </si>
+  <si>
+    <t>Der Bericht hebt Schutzbarrieren, Absturzsicherungen und klarere bildgestützte Arbeitsanweisungen bei Gamma Chimica hervor. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Kann verbessert werden</t>
+  </si>
+  <si>
+    <t>Welche Gewohnheit zu Hause unterstützt SDG 3 am besten?</t>
+  </si>
+  <si>
+    <t>Chemikalien und Medikamente sicher aufbewahren</t>
+  </si>
+  <si>
+    <t>Warnhinweise ignorieren</t>
+  </si>
+  <si>
+    <t>Gefahren für jemand anderen liegen lassen</t>
+  </si>
+  <si>
+    <t>Reinigungsmittel mischen, um sie stärker zu machen</t>
+  </si>
+  <si>
+    <t>Eine sichere Aufbewahrung verhindert Unfälle und schützt Menschen zu Hause. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Welche Entscheidung im Privatleben trägt zum Wohlbefinden bei?</t>
+  </si>
+  <si>
+    <t>Nie um Hilfe bitten</t>
+  </si>
+  <si>
+    <t>Regelmäßige Bewegung und ausreichend Erholung</t>
+  </si>
+  <si>
+    <t>Pausen immer auslassen</t>
+  </si>
+  <si>
+    <t>Stresssignale ignorieren</t>
+  </si>
+  <si>
+    <t>Körperliche Aktivität, Erholung und die Bitte um Unterstützung tragen zum Wohlbefinden bei. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
     <t>Quelle est l'idée principale de l'ODD 3 – Bonne santé et bien-être ?</t>
   </si>
   <si>
@@ -146,6 +698,81 @@
     <t>D'accord</t>
   </si>
   <si>
+    <t>Pourquoi l'ODD 3 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité ne concerne que les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que la manipulation sûre des produits chimiques peut influencer la performance en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n'ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>La manipulation sûre des produits chimiques est un domaine concret dans lequel une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante au sujet de l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Les collaborateurs peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>Seuls les hôpitaux sont responsables de la santé.</t>
+  </si>
+  <si>
+    <t>L'ODD 3 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>Voici l'idée fausse : elle réduit trop la portée de l'ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée reçue, car cela rend l'apprentissage mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement permet le mieux de faire passer l'ODD 3 de la théorie à l'action ?</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne vérifie.</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu'un d'autre règle tout.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mener à bien.</t>
+  </si>
+  <si>
+    <t>Une action concrète favorise l'apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Pourquoi l'ODD 3 constitue-t-il un sujet d'apprentissage utile pour les collaborateurs ?</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Il fournit une réponse parfaite pour chaque situation.</t>
+  </si>
+  <si>
+    <t>Il supprime la nécessité de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>Il n'a aucun rapport avec la culture d'entreprise.</t>
+  </si>
+  <si>
+    <t>L'apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et des choix familiers. Les ODD sont plus motivants lorsqu'ils paraissent pertinents, concrets et liés au rôle de chacun.</t>
+  </si>
+  <si>
     <t>Quelle est l'ambition déclarée de STOCKMEIER en matière de sécurité ?</t>
   </si>
   <si>
@@ -164,6 +791,84 @@
     <t>Le rapport énonce une ambition de zéro accident lié au travail et de zéro effet nocif sur la santé. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
   </si>
   <si>
+    <t>Quel résultat communiqué soutient le suivi de la santé au travail ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>Les accidents ne sont pas enregistrés</t>
+  </si>
+  <si>
+    <t>Seuls les responsables reçoivent des informations sur la sécurité</t>
+  </si>
+  <si>
+    <t>100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité</t>
+  </si>
+  <si>
+    <t>La sécurité n'est mesurée qu'une fois tous les dix ans</t>
+  </si>
+  <si>
+    <t>Le rapport indique que 100 % des personnes sont couvertes par des systèmes de management de la santé et de la sécurité. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quelle action de Gamma Chimica constitue une amélioration concrète de la sécurité ?</t>
+  </si>
+  <si>
+    <t>Réduire la communication sur les risques</t>
+  </si>
+  <si>
+    <t>Cesser de signaler les quasi-accidents</t>
+  </si>
+  <si>
+    <t>Supprimer toutes les instructions de travail</t>
+  </si>
+  <si>
+    <t>Des barrières de protection et des systèmes antichute</t>
+  </si>
+  <si>
+    <t>Le rapport met en avant les barrières de protection, les systèmes antichute et des instructions de travail illustrées plus claires chez Gamma Chimica. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Peut être amélioré</t>
+  </si>
+  <si>
+    <t>À la maison, quelle habitude soutient le mieux l'ODD 3 ?</t>
+  </si>
+  <si>
+    <t>Ranger les produits chimiques et les médicaments en toute sécurité</t>
+  </si>
+  <si>
+    <t>Ignorer les étiquettes d'avertissement</t>
+  </si>
+  <si>
+    <t>Laisser les dangers à quelqu'un d'autre</t>
+  </si>
+  <si>
+    <t>Mélanger des produits de nettoyage pour les rendre plus puissants</t>
+  </si>
+  <si>
+    <t>Un rangement sûr prévient les accidents et protège les personnes à la maison. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Quel choix dans la vie privée contribue au bien-être ?</t>
+  </si>
+  <si>
+    <t>Ne jamais demander d'aide</t>
+  </si>
+  <si>
+    <t>Bouger régulièrement et se reposer suffisamment</t>
+  </si>
+  <si>
+    <t>Toujours sauter les pauses</t>
+  </si>
+  <si>
+    <t>Ignorer les signes de stress</t>
+  </si>
+  <si>
+    <t>L'activité physique, le repos et le fait de demander du soutien contribuent au bien-être. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
     <t>¿Cuál es la idea principal del ODS 3 – Salud y bienestar?</t>
   </si>
   <si>
@@ -188,6 +893,81 @@
     <t>De acuerdo</t>
   </si>
   <si>
+    <t>¿Por qué es relevante el ODS 3 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Medio · Opción única</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo pertenece a los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque la manipulación segura de productos químicos puede influir en el desempeño en sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>La manipulación segura de productos químicos es un ámbito práctico en el que una empresa puede marcar la diferencia. Los ODS conectan los objetivos globales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido habitual sobre el ODS 3?</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>Solo los hospitales son responsables de la salud.</t>
+  </si>
+  <si>
+    <t>El ODS 3 puede vincularse a las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: limita demasiado el ODS y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar una idea errónea, porque así el aprendizaje resulta memorable.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 3 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está comprobándolo.</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>Esperar hasta que otra persona lo solucione todo.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio de comportamiento práctico.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 3 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>Relaciona los desafíos globales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura empresarial.</t>
+  </si>
+  <si>
+    <t>El aprendizaje es más sólido cuando las personas ven el vínculo entre los objetivos globales y las decisiones conocidas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y conectados con las funciones de las personas.</t>
+  </si>
+  <si>
     <t>¿Cuál es la ambición declarada de STOCKMEIER en relación con la seguridad?</t>
   </si>
   <si>
@@ -206,6 +986,84 @@
     <t>El informe establece la ambición de cero accidentes laborales y cero efectos perjudiciales para la salud. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
   </si>
   <si>
+    <t>¿Qué resultado comunicado respalda el seguimiento de la salud laboral?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>Los accidentes no se registran</t>
+  </si>
+  <si>
+    <t>Solo los directivos reciben información sobre seguridad</t>
+  </si>
+  <si>
+    <t>El 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad</t>
+  </si>
+  <si>
+    <t>La seguridad se mide solo una vez cada diez años</t>
+  </si>
+  <si>
+    <t>El informe indica que el 100 % de las personas está cubierto por sistemas de gestión de salud y seguridad. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué acción de Gamma Chimica supone una mejora práctica de la seguridad?</t>
+  </si>
+  <si>
+    <t>Reducir la comunicación sobre los riesgos</t>
+  </si>
+  <si>
+    <t>Dejar de informar sobre cuasiaccidentes</t>
+  </si>
+  <si>
+    <t>Eliminar todas las instrucciones de trabajo</t>
+  </si>
+  <si>
+    <t>Barreras de protección y sistemas anticaídas</t>
+  </si>
+  <si>
+    <t>El informe destaca las barreras de protección, los sistemas anticaídas y unas instrucciones de trabajo con imágenes más claras en Gamma Chimica. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>Puede mejorarse</t>
+  </si>
+  <si>
+    <t>En casa, ¿qué hábito apoya mejor el ODS 3?</t>
+  </si>
+  <si>
+    <t>Guardar de forma segura los productos químicos y los medicamentos</t>
+  </si>
+  <si>
+    <t>Ignorar las etiquetas de advertencia</t>
+  </si>
+  <si>
+    <t>Dejar los peligros para otra persona</t>
+  </si>
+  <si>
+    <t>Mezclar productos de limpieza para hacerlos más fuertes</t>
+  </si>
+  <si>
+    <t>El almacenamiento seguro evita accidentes y protege a las personas en casa. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Qué elección en la vida privada contribuye al bienestar?</t>
+  </si>
+  <si>
+    <t>No pedir ayuda nunca</t>
+  </si>
+  <si>
+    <t>Actividad física regular y descanso adecuado</t>
+  </si>
+  <si>
+    <t>Saltarse siempre las pausas</t>
+  </si>
+  <si>
+    <t>Ignorar las señales de estrés</t>
+  </si>
+  <si>
+    <t>La actividad física, el descanso y pedir apoyo contribuyen al bienestar. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
     <t>Qual è l'idea principale alla base dell'SDG 3 – Salute e benessere?</t>
   </si>
   <si>
@@ -230,6 +1088,81 @@
     <t>Va bene</t>
   </si>
   <si>
+    <t>Perché l'SDG 3 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Risposta singola</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità riguarda soltanto i rapporti annuali.</t>
+  </si>
+  <si>
+    <t>Perché la manipolazione sicura dei prodotti chimici può influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli SDG sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>La manipolazione sicura dei prodotti chimici è un ambito concreto in cui un'azienda può fare la differenza. Gli SDG collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull'SDG 3?</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>Solo gli ospedali sono responsabili della salute.</t>
+  </si>
+  <si>
+    <t>L'SDG 3 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo l'SDG e nasconde opportunità concrete. Una buona domanda di un quiz spesso mette in discussione un'idea errata, perché rende memorabile l'apprendimento.</t>
+  </si>
+  <si>
+    <t>Quale comportamento trasforma meglio l'SDG 3 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico del comportamento.</t>
+  </si>
+  <si>
+    <t>Cosa rende l'SDG 3 un argomento formativo utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Fornisce una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>Non ha alcun rapporto con la cultura aziendale.</t>
+  </si>
+  <si>
+    <t>L'apprendimento è più efficace quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli SDG sono più coinvolgenti quando appaiono rilevanti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
     <t>Qual è l'ambizione dichiarata di STOCKMEIER in materia di sicurezza?</t>
   </si>
   <si>
@@ -248,7 +1181,82 @@
     <t>Il rapporto dichiara l'ambizione di zero infortuni sul lavoro e zero effetti nocivi sulla salute. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
   </si>
   <si>
-    <t>Jaka jest główna idea SDG 3 – Dobre zdrowie i jakość życia?</t>
+    <t>Quale risultato riportato supporta il monitoraggio della salute sul lavoro?</t>
+  </si>
+  <si>
+    <t>Difficile · Risposta singola</t>
+  </si>
+  <si>
+    <t>Gli incidenti non vengono registrati</t>
+  </si>
+  <si>
+    <t>Solo i dirigenti ricevono informazioni sulla sicurezza</t>
+  </si>
+  <si>
+    <t>Il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza</t>
+  </si>
+  <si>
+    <t>La sicurezza viene misurata soltanto una volta ogni dieci anni</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che il 100% delle persone è coperto da sistemi di gestione della salute e della sicurezza. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale azione di Gamma Chimica rappresenta un miglioramento pratico della sicurezza?</t>
+  </si>
+  <si>
+    <t>Ridurre la comunicazione sui rischi</t>
+  </si>
+  <si>
+    <t>Interrompere la segnalazione dei mancati incidenti</t>
+  </si>
+  <si>
+    <t>Rimuovere tutte le istruzioni di lavoro</t>
+  </si>
+  <si>
+    <t>Barriere protettive e sistemi anticaduta</t>
+  </si>
+  <si>
+    <t>Il rapporto evidenzia barriere protettive, sistemi anticaduta e istruzioni di lavoro illustrate più chiare presso Gamma Chimica. Gli esempi di STOCKMEIER rendono concreto l'SDG e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Può essere migliorato</t>
+  </si>
+  <si>
+    <t>A casa, quale abitudine supporta meglio l'SDG 3?</t>
+  </si>
+  <si>
+    <t>Conservare in modo sicuro prodotti chimici e medicinali</t>
+  </si>
+  <si>
+    <t>Ignorare le etichette di avvertimento</t>
+  </si>
+  <si>
+    <t>Lasciare i pericoli a qualcun altro</t>
+  </si>
+  <si>
+    <t>Mescolare prodotti per la pulizia per renderli più forti</t>
+  </si>
+  <si>
+    <t>Una conservazione sicura previene gli incidenti e protegge le persone a casa. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale scelta nella vita privata contribuisce al benessere?</t>
+  </si>
+  <si>
+    <t>Non chiedere mai aiuto</t>
+  </si>
+  <si>
+    <t>Movimento regolare e riposo adeguato</t>
+  </si>
+  <si>
+    <t>Saltare sempre le pause</t>
+  </si>
+  <si>
+    <t>Ignorare i segnali di stress</t>
+  </si>
+  <si>
+    <t>L'attività fisica, il riposo e la richiesta di sostegno contribuiscono al benessere. Le abitudini personali sono importanti perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
   <si>
     <t>Łatwe · Jedna odpowiedź</t>
@@ -272,7 +1280,67 @@
     <t>W porządku</t>
   </si>
   <si>
-    <t>Jaką ambicję dotyczącą bezpieczeństwa deklaruje STOCKMEIER?</t>
+    <t>Średnie · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój ma miejsce wyłącznie w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ bezpieczne obchodzenie się z chemikaliami może wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Ponieważ SDG zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Bezpieczne obchodzenie się z chemikaliami jest praktycznym obszarem, w którym firma może coś zmienić. SDG łączą globalne cele z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne codzienne nawyki.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i ograniczać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>Za zdrowie odpowiadają wyłącznie szpitale.</t>
+  </si>
+  <si>
+    <t>SDG 3 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>To błędne przekonanie nadmiernie zawęża zakres SDG i przesłania praktyczne możliwości działania. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu wiedza lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Postępowanie odwrotnie, gdy nikt nie sprawdza.</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne wdrożenie go.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie sprzyja uczeniu się i prowadzi do wymiernej poprawy. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowań.</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami, które ludzie rozpoznają w pracy i w domu.</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź na każdą sytuację.</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę posiadania wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą organizacyjną.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsza nauka zachodzi wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi im wyborami. SDG najbardziej angażują, gdy są istotne, konkretne i powiązane z rolami poszczególnych osób.</t>
   </si>
   <si>
     <t>Zastąpienie wszystkich szkoleń z zakresu bezpieczeństwa plakatami</t>
@@ -290,104 +1358,122 @@
     <t>W raporcie określono ambicję osiągnięcia zerowej liczby wypadków związanych z pracą oraz zerowego szkodliwego wpływu na zdrowie. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
   </si>
   <si>
-    <t>What does sustainability in everyday work mean most of all?</t>
-  </si>
-  <si>
-    <t>Single choice</t>
-  </si>
-  <si>
-    <t>Only large projects matter, not small daily decisions.</t>
-  </si>
-  <si>
-    <t>Sustainability is an ongoing process that we can support every day.</t>
-  </si>
-  <si>
-    <t>Sustainability only concerns environmental departments and managers.</t>
-  </si>
-  <si>
-    <t>Sustainability is a topic for later, not for today's work.</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>The report describes sustainability as a daily path, not a one-time goal.</t>
-  </si>
-  <si>
-    <t>multiple</t>
-  </si>
-  <si>
-    <t>Which goals fit the “Zero in Focus” idea?</t>
-  </si>
-  <si>
-    <t>Multiple choice</t>
-  </si>
-  <si>
-    <t>Zero CO₂ emissions</t>
-  </si>
-  <si>
-    <t>Zero accidents at work</t>
-  </si>
-  <si>
-    <t>Zero tolerance for unethical behaviour</t>
-  </si>
-  <si>
-    <t>Zero training</t>
-  </si>
-  <si>
-    <t>0,1,2</t>
-  </si>
-  <si>
-    <t>The idea combines climate, safety and integrity. Training is not a “Zero” goal.</t>
-  </si>
-  <si>
-    <t>Was bedeutet Nachhaltigkeit im Arbeitsalltag vor allem?</t>
-  </si>
-  <si>
-    <t>Einfachauswahl</t>
-  </si>
-  <si>
-    <t>Nur große Projekte zählen, nicht kleine tägliche Entscheidungen.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein fortlaufender Prozess, den wir jeden Tag unterstützen können.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit betrifft nur Umweltabteilungen und Führungskräfte.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein Thema für später, nicht für die heutige Arbeit.</t>
-  </si>
-  <si>
-    <t>Der Bericht beschreibt Nachhaltigkeit als einen täglichen Weg und nicht als einmaliges Ziel.</t>
-  </si>
-  <si>
-    <t>Welche Ziele passen zur Idee „Zero in Focus“?</t>
-  </si>
-  <si>
-    <t>Mehrfachauswahl</t>
-  </si>
-  <si>
-    <t>Null CO₂-Emissionen</t>
-  </si>
-  <si>
-    <t>Null Arbeitsunfälle</t>
-  </si>
-  <si>
-    <t>Null Toleranz gegenüber unethischem Verhalten</t>
-  </si>
-  <si>
-    <t>Null Schulungen</t>
-  </si>
-  <si>
-    <t>Die Idee verbindet Klima, Sicherheit und Integrität. Schulungen sind kein „Zero“-Ziel.</t>
+    <t>Trudne · Jedna odpowiedź</t>
+  </si>
+  <si>
+    <t>Wypadki nie są rejestrowane</t>
+  </si>
+  <si>
+    <t>Tylko kadra kierownicza otrzymuje informacje dotyczące bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy</t>
+  </si>
+  <si>
+    <t>Bezpieczeństwo jest mierzone tylko raz na dziesięć lat</t>
+  </si>
+  <si>
+    <t>W raporcie stwierdzono, że 100% osób jest objętych systemami zarządzania bezpieczeństwem i higieną pracy. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Ograniczenie komunikacji na temat ryzyka</t>
+  </si>
+  <si>
+    <t>Zaprzestanie zgłaszania zdarzeń potencjalnie wypadkowych</t>
+  </si>
+  <si>
+    <t>Usunięcie wszystkich instrukcji pracy</t>
+  </si>
+  <si>
+    <t>Bariery ochronne i systemy zabezpieczające przed upadkiem</t>
+  </si>
+  <si>
+    <t>W raporcie podkreślono zastosowanie w Gamma Chimica barier ochronnych, zabezpieczeń przed upadkiem oraz bardziej przejrzystych instrukcji pracy opartych na ilustracjach. Przykłady ze STOCKMEIER konkretyzują SDG i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Można poprawić</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie chemikaliów i leków</t>
+  </si>
+  <si>
+    <t>Ignorowanie etykiet ostrzegawczych</t>
+  </si>
+  <si>
+    <t>Pozostawianie zagrożeń do usunięcia komuś innemu</t>
+  </si>
+  <si>
+    <t>Mieszanie środków czyszczących, aby zwiększyć ich siłę działania</t>
+  </si>
+  <si>
+    <t>Bezpieczne przechowywanie zapobiega wypadkom i chroni ludzi w domu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Nieproszenie nigdy o pomoc</t>
+  </si>
+  <si>
+    <t>Regularna aktywność fizyczna i odpowiedni odpoczynek</t>
+  </si>
+  <si>
+    <t>Ciągłe pomijanie przerw</t>
+  </si>
+  <si>
+    <t>Ignorowanie sygnałów stresu</t>
+  </si>
+  <si>
+    <t>Aktywność fizyczna, odpoczynek i proszenie o wsparcie przyczyniają się do dobrostanu. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Why is SDG 3 – Good Health and Well-Being relevant for a chemical distribution and production company?</t>
+  </si>
+  <si>
+    <t>Which statement is a common misunderstanding about SDG 3 – Good Health and Well-Being?</t>
+  </si>
+  <si>
+    <t>Which behaviour best turns SDG 3 – Good Health and Well-Being from theory into action?</t>
+  </si>
+  <si>
+    <t>What makes SDG 3 – Good Health and Well-Being a useful learning topic for employees?</t>
+  </si>
+  <si>
+    <t>At home, which habit best supports SDG 3 – Good Health and Well-Being?</t>
+  </si>
+  <si>
+    <t>Na czym polega główna idea SDG 3 – Dobre zdrowie i jakość życia?</t>
+  </si>
+  <si>
+    <t>Dlaczego SDG 3 – Dobre zdrowie i jakość życia ma znaczenie dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie odzwierciedla powszechne błędne przekonanie dotyczące SDG 3 – Dobre zdrowie i jakość życia?</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada założenia SDG 3 – Dobre zdrowie i jakość życia z teorii na konkretne działania?</t>
+  </si>
+  <si>
+    <t>Dlaczego SDG 3 – Dobre zdrowie i jakość życia jest wartościowym tematem szkoleniowym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Jaką ambicję w zakresie bezpieczeństwa deklaruje STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Który z wyników przedstawionych w raporcie wspiera monitorowanie zdrowia pracowników?</t>
+  </si>
+  <si>
+    <t>Które działanie firmy Gamma Chimica stanowi praktyczne usprawnienie w zakresie bezpieczeństwa?</t>
+  </si>
+  <si>
+    <t>Który nawyk domowy najlepiej wspiera SDG 3 – Dobre zdrowie i jakość życia?</t>
+  </si>
+  <si>
+    <t>Który wybór w życiu prywatnym przyczynia się do dobrostanu?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +1485,16 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -476,22 +1572,28 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D8D4"/>
-      </bottom>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -500,262 +1602,97 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="50">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FFD8D8D4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1127,75 +2064,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1209,19 +2077,23 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J3">
-  <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1229,114 +2101,114 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="61">
-  <autoFilter ref="A1:J3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="Column8"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}" name="Questions_FR" displayName="Questions_FR" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="27"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J3" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
-  <autoFilter ref="A1:J3" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+  <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="16"/>
     <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J3" totalsRowShown="0">
-  <autoFilter ref="A1:J3" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="13"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="9"/>
     <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J3">
-  <autoFilter ref="A1:J3" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
     <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1627,8 +2499,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -1639,7 +2511,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1671,68 +2543,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>89</v>
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>98</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1745,112 +2873,368 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="100" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
+      <c r="B2" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>72</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>80</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
+      <c r="I3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1863,19 +3247,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1907,68 +3291,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
+      <c r="B2" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>211</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
+      <c r="B3" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>38</v>
+        <v>219</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>33</v>
+      <c r="I3" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -1981,112 +3621,368 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="47.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="7" width="34.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="56.42578125" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="56.36328125" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="4">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="H2" s="6">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="I2" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>75</v>
+      <c r="I3" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H4" s="6">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="H5" s="9">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="H9" s="9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -2099,19 +3995,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2143,68 +4039,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>40</v>
+      <c r="B2" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>276</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>48</v>
+      <c r="B3" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>284</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>47</v>
+      <c r="I3" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2217,19 +4369,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2261,68 +4413,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>54</v>
+      <c r="B2" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>341</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="I2" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>62</v>
+      <c r="B3" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>349</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>61</v>
+      <c r="I3" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -2335,19 +4743,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2379,68 +4787,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>105</v>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>112</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2452,6 +5116,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -2615,26 +5298,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2650,22 +5332,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E1F90F-679A-4B57-A7C5-A373B94A5194}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F19F1512-86DB-4AD0-AA3F-331DCE8392A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="465">
   <si>
     <t>type</t>
   </si>
@@ -450,36 +450,6 @@
   </si>
   <si>
     <t>Lichaamsbeweging, rust en om steun vragen dragen bij aan welzijn. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
-  </si>
-  <si>
-    <t>Column6</t>
-  </si>
-  <si>
-    <t>Column7</t>
-  </si>
-  <si>
-    <t>Column8</t>
-  </si>
-  <si>
-    <t>Column9</t>
-  </si>
-  <si>
-    <t>Column10</t>
   </si>
   <si>
     <t>Was ist die zentrale Idee hinter SDG 3 – Gesundheit und Wohlergehen?</t>
@@ -1582,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1626,11 +1596,30 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="57">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1638,25 +1627,126 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1779,10 +1869,44 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1830,74 +1954,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1960,37 +2016,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
@@ -2077,10 +2102,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
   <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -2092,7 +2113,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct" dataDxfId="16"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
   </tableColumns>
@@ -2101,19 +2122,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="Column2" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="Column4" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="Column5" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="Column6" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="Column7" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="Column8"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="Column9" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Column10" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2124,34 +2145,34 @@
   <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="39"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2162,15 +2183,15 @@
   <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="34"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2181,15 +2202,15 @@
   <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="29"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2200,15 +2221,15 @@
   <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="24"/>
     <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
-    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2500,18 +2521,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" style="20" customWidth="1"/>
     <col min="9" max="9" width="75" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2533,7 +2554,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -2543,7 +2564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2565,7 +2586,7 @@
       <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="19">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -2575,12 +2596,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -2597,7 +2618,7 @@
       <c r="G3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="19">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2607,12 +2628,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>12</v>
@@ -2629,7 +2650,7 @@
       <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="19">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -2639,12 +2660,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -2661,7 +2682,7 @@
       <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="19">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -2671,12 +2692,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -2693,7 +2714,7 @@
       <c r="G6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="19">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -2703,7 +2724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2725,7 +2746,7 @@
       <c r="G7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="19">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -2735,7 +2756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2757,7 +2778,7 @@
       <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="19">
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -2767,7 +2788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2789,7 +2810,7 @@
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="19">
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -2799,12 +2820,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>12</v>
@@ -2821,7 +2842,7 @@
       <c r="G10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="19">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -2831,7 +2852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2853,7 +2874,7 @@
       <c r="G11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="19">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -2874,50 +2895,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2939,7 +2960,7 @@
       <c r="G2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="20">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -2949,7 +2970,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2971,7 +2992,7 @@
       <c r="G3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="20">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -2981,7 +3002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3003,7 +3024,7 @@
       <c r="G4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="20">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -3013,7 +3034,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3035,7 +3056,7 @@
       <c r="G5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="20">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -3045,7 +3066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3067,7 +3088,7 @@
       <c r="G6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="20">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -3077,7 +3098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3099,7 +3120,7 @@
       <c r="G7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="20">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -3109,7 +3130,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3131,7 +3152,7 @@
       <c r="G8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="20">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -3141,7 +3162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3163,7 +3184,7 @@
       <c r="G9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="20">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -3173,7 +3194,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3195,7 +3216,7 @@
       <c r="G10" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="20">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -3205,7 +3226,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3227,7 +3248,7 @@
       <c r="G11" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="20">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -3248,18 +3269,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3281,7 +3302,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -3291,324 +3312,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H3" s="20">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J3" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H2">
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H4" s="20">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="20">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H6" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H3">
+      <c r="I6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H7" s="20">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H4">
+      <c r="I7" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H8" s="20">
         <v>3</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H5">
+      <c r="I8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H9" s="20">
         <v>4</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="H6">
+      <c r="I9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H10" s="20">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H7">
+      <c r="I10" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="H11" s="20">
         <v>2</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="I11" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3622,18 +3643,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="34.54296875" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="56.36328125" customWidth="1"/>
-    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="47.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="7" width="34.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="56.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3665,324 +3686,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="H2" s="15">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="H3" s="16">
+        <v>2</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="J3" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="H2" s="6">
+      <c r="F4" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="H4" s="15">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="H5" s="16">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H6" s="15">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="I6" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="H7" s="16">
         <v>2</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="I7" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H8" s="15">
         <v>3</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="H5" s="9">
+      <c r="I8" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="H9" s="16">
         <v>4</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="I9" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="H10" s="15">
         <v>1</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="I10" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="H11" s="17">
         <v>2</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="I11" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>439</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="H8" s="6">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H9" s="9">
-        <v>4</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="H11" s="12">
-        <v>2</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -3996,18 +4017,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4029,7 +4050,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4039,324 +4060,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H3" s="20">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J3" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="H2">
+      <c r="C4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="H4" s="20">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="H5" s="20">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="H3">
+      <c r="I6" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H7" s="20">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H4">
+      <c r="I7" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H8" s="20">
         <v>3</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="H5">
+      <c r="I8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9" s="20">
         <v>4</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="C6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H6">
+      <c r="I9" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" s="20">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C7" t="s">
-        <v>276</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="H7">
+      <c r="I10" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H11" s="20">
         <v>2</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="I11" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C9" t="s">
-        <v>315</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C10" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C11" t="s">
-        <v>276</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4370,18 +4391,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4403,7 +4424,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4413,324 +4434,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H3" s="20">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J3" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="H2">
+      <c r="C4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H4" s="20">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H5" s="20">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="H6" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="C3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="H3">
+      <c r="I6" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H7" s="20">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="H4">
+      <c r="I7" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H8" s="20">
         <v>3</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="H5">
+      <c r="I8" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="H9" s="20">
         <v>4</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C6" t="s">
-        <v>349</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="H6">
+      <c r="I9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H10" s="20">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="H7">
+      <c r="I10" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H11" s="20">
         <v>2</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C8" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="I11" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>382</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C9" t="s">
-        <v>380</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="C10" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C11" t="s">
-        <v>341</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -4744,18 +4765,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.08984375" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4777,7 +4798,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -4787,324 +4808,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H2" s="2">
+        <v>141</v>
+      </c>
+      <c r="H2" s="19">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="2">
+        <v>148</v>
+      </c>
+      <c r="H3" s="19">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H4" s="2">
+        <v>154</v>
+      </c>
+      <c r="H4" s="19">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" s="2">
+        <v>160</v>
+      </c>
+      <c r="H5" s="19">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H6" s="2">
+        <v>166</v>
+      </c>
+      <c r="H6" s="19">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H7" s="2">
+        <v>172</v>
+      </c>
+      <c r="H7" s="19">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H8" s="2">
+        <v>179</v>
+      </c>
+      <c r="H8" s="19">
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" s="19">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="H10" s="19">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="J10" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H9" s="2">
-        <v>4</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="H11" s="19">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5116,25 +5137,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -5298,25 +5300,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052D775B-35AE-4D8C-85B8-39FE1C3B4BBC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5332,4 +5335,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A12AD6-4D28-47C9-A756-6744BC5075CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A947F87A-A862-469B-80AB-EC8D5B706ABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Questions - Round 1.xlsx
+++ b/Questions - Round 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz-TEST/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F19F1512-86DB-4AD0-AA3F-331DCE8392A2}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="11_DC4634EEB09B7631DD1D459FDEF3484CE4F5FC66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{945B78D8-D07F-4CE8-9FBD-CD453FDD24D8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -1552,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1596,29 +1596,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="50">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1627,7 +1611,7 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1636,117 +1620,13 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1856,6 +1736,71 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2113,7 +2058,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
   </tableColumns>
@@ -2122,19 +2067,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{F33C372F-7DF1-44B8-A553-F96162E20FF6}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8768A190-4619-4E99-A1FB-E085A0691535}" name="type"/>
-    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{138753B1-3E1C-449D-94EC-F0C2EEB45A70}" name="question" dataDxfId="34"/>
     <tableColumn id="3" xr3:uid="{FED00481-A20D-41CA-B9AD-1BEC5A6526F9}" name="note"/>
-    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{4C97B040-4120-4B99-933B-CBD2000E9533}" name="option1" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{2A6AFBEF-0DA7-467B-A43E-90728CFDE3FA}" name="option2" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{C01A211B-00E9-4EAC-B1E5-E7E8A3AC81EB}" name="option3" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{AD151611-2D1E-44FE-BA77-0142DB062F48}" name="option4" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{7E796F1C-08BD-41F7-8EAA-7AE75851648A}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{71BF8262-57EB-411D-86D6-D11A0BCDCFA5}" name="explanation" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{1E13442E-16C8-44FA-B52D-99CDBBFE4D11}" name="Comments ZF" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2145,34 +2090,34 @@
   <autoFilter ref="A1:J11" xr:uid="{0443C156-3373-4BEF-9D5B-BE15850933BA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F437D6E2-54A8-46CF-B6AA-72B1DDDBD98E}" name="type"/>
-    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{952F0744-7AAB-463E-BCD7-2E26EA55F0B5}" name="question" dataDxfId="27"/>
     <tableColumn id="3" xr3:uid="{2B1FC043-0C02-4B8E-9EEB-67C6FA02E0F8}" name="note"/>
-    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{EAD83E31-505A-42DC-942F-F9E48303E96B}" name="option1" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{C9E5F8DA-09FA-45D4-B2F9-7D4E6C797F1B}" name="option2" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{4F227AFF-14FF-495C-A638-834DE2F2F0F1}" name="option3" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{03B75AA8-AED7-4944-9BBB-FA1CDA99CE3C}" name="option4" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{A9DB8E5B-B50B-451E-80E7-BC3C1E2EB942}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{596E4A30-D592-45A2-9BA6-909C7233F36E}" name="explanation" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{E0D67ADC-A9CC-4A55-ABB2-99CF33216FD1}" name="Comments ZF" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A1:J11" xr:uid="{44E0FAA6-8BD7-4759-AAA3-94BECD54F540}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{B8E1CEFB-D4F5-4454-8EE2-4CC13B41524D}" name="type" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{0B3BB530-19FC-4EF1-8906-128ED72B0CF4}" name="question" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{A026DC58-89E8-41A8-87BF-377C94896F3B}" name="note" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{E52F3421-7180-4A31-AD6A-7C5921781982}" name="option1" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{50128664-5FE2-4CA5-B1A5-9B8B853A2B64}" name="option2" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{57AC2722-D37E-4A00-8697-571E06CE666D}" name="option3" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{6127D6A3-5DD7-4DBA-B556-18BCAA69EB40}" name="option4" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{8345AB07-2F86-429A-A477-BB8EC49876B0}" name="correct" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{E51614FA-9BED-41B9-8BFE-5ED5998D9CA0}" name="explanation" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{0BD74B70-C4EA-40E7-8E13-D86793442E46}" name="Comments ZF" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2183,15 +2128,15 @@
   <autoFilter ref="A1:J11" xr:uid="{24328404-240E-47C6-99B4-84D4666E487C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D28DA00C-53DD-41D8-A3BF-DB525A0D4771}" name="type"/>
-    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{175F879F-6B11-4B9A-8454-1120A2D79E3F}" name="question" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{F21BF042-E407-4DB9-A79D-DA0E245869A5}" name="note"/>
-    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{619CB46F-4592-4C56-A69F-68EB3309A9BB}" name="option1" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{50FBD72E-8E38-49CB-B7A5-F14034CD6617}" name="option2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{26B75C25-0F86-4BC5-A8FD-E52ECDA5672E}" name="option3" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{A923C1B9-61C5-420B-883C-04A0A11B7BC5}" name="option4" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{6F0FFD5B-A111-4E68-B09A-F9C8C262B0AE}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{2ABE4738-C112-4F9E-8A03-64A555F8DFCB}" name="explanation" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{6886EBCC-E8F2-4112-BF52-377F836CE96C}" name="Comments ZF" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2202,15 +2147,15 @@
   <autoFilter ref="A1:J11" xr:uid="{69487D5A-D6BB-406F-B006-C23DC0801576}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{11EBFC79-7169-44C9-98FF-AEAD54A3F4CF}" name="type"/>
-    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{D15870D6-4160-450D-8A48-A45F378320C5}" name="question" dataDxfId="13"/>
     <tableColumn id="3" xr3:uid="{5BC96237-C15E-4AF1-BB12-192ED4C16B04}" name="note"/>
-    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{A7B78417-59DE-4F90-81A8-EF0636F85EF1}" name="option1" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C10D44DD-CD72-49D7-AF76-3B9DBCC1FB72}" name="option2" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{D24F9622-47A3-40CF-8336-5D9ABAFAB985}" name="option3" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{E354F182-1976-4AA1-88B5-B44C580AD1F1}" name="option4" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{E6194F33-38E1-4D8F-AC4B-43D3240E8F29}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{52ABFCD8-07EF-429C-B7F4-3C69747A12F2}" name="explanation" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{6C0169E4-F1E8-4B5D-BE55-5684B57CF5ED}" name="Comments ZF" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2221,15 +2166,15 @@
   <autoFilter ref="A1:J11" xr:uid="{03F5E4B0-1EE4-4A96-B063-5B136C1A51C8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6EBC16CA-B01C-4958-B5F0-385E02F2076F}" name="type"/>
-    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{17A07ACE-7C03-46F0-BB3C-0E2AEBB60E87}" name="question" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{21C55411-3486-4BC8-BDEB-1355F960228C}" name="note"/>
-    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{3DC4C62B-B6B5-4550-B418-91D15C90EF11}" name="option1" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{A93353C8-8D88-4219-903B-30B1C42FF339}" name="option2" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{FB6C5E79-096F-4610-A1AF-1E2713100CE6}" name="option3" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{C83EC64E-DF84-427F-92DC-1D91223EB6AE}" name="option4" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{6B2FC0C7-D58D-4EEE-9847-3B9CF8F4FCCA}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{C2B6DEC7-7756-44AE-8BB4-CBF8A804D904}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{62EB005F-AEC9-4EB3-B430-68004B533DA8}" name="Comments ZF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2521,18 +2466,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="12" style="20" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="75" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2554,7 +2499,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -2564,7 +2509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2586,7 +2531,7 @@
       <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -2596,7 +2541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2618,7 +2563,7 @@
       <c r="G3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2628,7 +2573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2650,7 +2595,7 @@
       <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="2">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -2660,7 +2605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2682,7 +2627,7 @@
       <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -2692,7 +2637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2714,7 +2659,7 @@
       <c r="G6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -2724,7 +2669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2746,7 +2691,7 @@
       <c r="G7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -2756,7 +2701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2778,7 +2723,7 @@
       <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="2">
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -2788,7 +2733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2810,7 +2755,7 @@
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="2">
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -2820,7 +2765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2842,7 +2787,7 @@
       <c r="G10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -2852,7 +2797,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2874,7 +2819,7 @@
       <c r="G11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="2">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -2895,50 +2840,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227CF05-7239-4F54-B608-C703C72C3BAC}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="100" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2960,7 +2905,7 @@
       <c r="G2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -2970,7 +2915,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2992,7 +2937,7 @@
       <c r="G3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -3002,7 +2947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3024,7 +2969,7 @@
       <c r="G4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -3034,7 +2979,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3056,7 +3001,7 @@
       <c r="G5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -3066,7 +3011,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3088,7 +3033,7 @@
       <c r="G6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -3098,7 +3043,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3120,7 +3065,7 @@
       <c r="G7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -3130,7 +3075,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3152,7 +3097,7 @@
       <c r="G8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -3162,7 +3107,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3184,7 +3129,7 @@
       <c r="G9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -3194,7 +3139,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3216,7 +3161,7 @@
       <c r="G10" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -3226,7 +3171,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3248,7 +3193,7 @@
       <c r="G11" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -3269,18 +3214,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1782B8D-F84F-48AC-9C34-ADAF5AFDA9A4}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3302,7 +3247,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -3312,7 +3257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3334,7 +3279,7 @@
       <c r="G2" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -3344,7 +3289,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3366,7 +3311,7 @@
       <c r="G3" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -3376,7 +3321,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3398,7 +3343,7 @@
       <c r="G4" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -3408,7 +3353,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3430,7 +3375,7 @@
       <c r="G5" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -3440,7 +3385,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3462,7 +3407,7 @@
       <c r="G6" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -3472,7 +3417,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3494,7 +3439,7 @@
       <c r="G7" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -3504,7 +3449,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3526,7 +3471,7 @@
       <c r="G8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -3536,7 +3481,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3558,7 +3503,7 @@
       <c r="G9" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -3568,7 +3513,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3590,7 +3535,7 @@
       <c r="G10" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -3600,7 +3545,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3622,7 +3567,7 @@
       <c r="G11" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -3643,18 +3588,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19654F59-BD48-4AA6-AB10-E1FF83EE6625}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="47.21875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="7" width="34.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="56.33203125" customWidth="1"/>
-    <col min="10" max="10" width="18.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="56.36328125" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3686,7 +3631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -3708,7 +3653,7 @@
       <c r="G2" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="6">
         <v>1</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -3718,7 +3663,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
@@ -3740,7 +3685,7 @@
       <c r="G3" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="9">
         <v>2</v>
       </c>
       <c r="I3" s="9" t="s">
@@ -3750,7 +3695,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
@@ -3772,7 +3717,7 @@
       <c r="G4" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="6">
         <v>3</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -3782,7 +3727,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
@@ -3804,7 +3749,7 @@
       <c r="G5" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="9">
         <v>4</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -3814,7 +3759,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -3836,7 +3781,7 @@
       <c r="G6" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -3846,7 +3791,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
@@ -3868,7 +3813,7 @@
       <c r="G7" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="9">
         <v>2</v>
       </c>
       <c r="I7" s="9" t="s">
@@ -3878,7 +3823,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -3900,7 +3845,7 @@
       <c r="G8" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="6">
         <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -3910,7 +3855,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
@@ -3932,7 +3877,7 @@
       <c r="G9" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="9">
         <v>4</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -3942,7 +3887,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
@@ -3964,7 +3909,7 @@
       <c r="G10" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="6">
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -3974,7 +3919,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
@@ -3996,7 +3941,7 @@
       <c r="G11" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="12">
         <v>2</v>
       </c>
       <c r="I11" s="12" t="s">
@@ -4017,18 +3962,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C93C6A-F93F-4793-BD9F-71A4EA325BA6}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4050,7 +3995,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4060,7 +4005,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4082,7 +4027,7 @@
       <c r="G2" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -4092,7 +4037,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +4059,7 @@
       <c r="G3" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -4124,7 +4069,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -4146,7 +4091,7 @@
       <c r="G4" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -4156,7 +4101,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4178,7 +4123,7 @@
       <c r="G5" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -4188,7 +4133,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4210,7 +4155,7 @@
       <c r="G6" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -4220,7 +4165,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4242,7 +4187,7 @@
       <c r="G7" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -4252,7 +4197,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4274,7 +4219,7 @@
       <c r="G8" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -4284,7 +4229,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -4306,7 +4251,7 @@
       <c r="G9" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -4316,7 +4261,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -4338,7 +4283,7 @@
       <c r="G10" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -4348,7 +4293,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4370,7 +4315,7 @@
       <c r="G11" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -4391,18 +4336,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48C580-F830-4656-B607-BD4517683869}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4424,7 +4369,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4434,7 +4379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4456,7 +4401,7 @@
       <c r="G2" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -4466,7 +4411,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4488,7 +4433,7 @@
       <c r="G3" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -4498,7 +4443,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -4520,7 +4465,7 @@
       <c r="G4" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -4530,7 +4475,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4552,7 +4497,7 @@
       <c r="G5" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -4562,7 +4507,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4584,7 +4529,7 @@
       <c r="G6" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -4594,7 +4539,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4616,7 +4561,7 @@
       <c r="G7" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -4626,7 +4571,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4648,7 +4593,7 @@
       <c r="G8" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8">
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -4658,7 +4603,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -4680,7 +4625,7 @@
       <c r="G9" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -4690,7 +4635,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -4712,7 +4657,7 @@
       <c r="G10" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -4722,7 +4667,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4744,7 +4689,7 @@
       <c r="G11" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
@@ -4765,18 +4710,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3985FE85-E541-4FD0-B389-FEC482BF15E7}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.08984375" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4798,7 +4743,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -4808,7 +4753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -4830,7 +4775,7 @@
       <c r="G2" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -4840,7 +4785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -4862,7 +4807,7 @@
       <c r="G3" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -4872,7 +4817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4894,7 +4839,7 @@
       <c r="G4" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="2">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -4904,7 +4849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4926,7 +4871,7 @@
       <c r="G5" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -4936,7 +4881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4958,7 +4903,7 @@
       <c r="G6" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -4968,7 +4913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4990,7 +4935,7 @@
       <c r="G7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -5000,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -5022,7 +4967,7 @@
       <c r="G8" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="2">
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -5032,7 +4977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -5054,7 +4999,7 @@
       <c r="G9" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="2">
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -5064,7 +5009,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -5086,7 +5031,7 @@
       <c r="G10" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -5096,7 +5041,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -5118,7 +5063,7 @@
       <c r="G11" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="2">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
